--- a/pelzer.xlsx
+++ b/pelzer.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFB21DEF-19A2-49C0-8C16-69FC0DFD9398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEA1DB1E-5834-4CA6-BF27-184B7AED894C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-10910" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carrier Route Scheme" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4076" uniqueCount="587">
   <si>
     <t>Scheme Listing by CRID for ZIP Code 29669</t>
   </si>
@@ -1775,7 +1775,7 @@
     <t>Total Line items: 508</t>
   </si>
   <si>
-    <t>ZIPE CODE</t>
+    <t>zip code</t>
   </si>
 </sst>
 </file>
@@ -2181,7 +2181,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -2239,7 +2239,7 @@
       <c r="G3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3">
         <v>29669</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -2268,7 +2268,7 @@
       <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4">
         <v>29669</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -2297,7 +2297,7 @@
       <c r="G5" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>29669</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -2326,7 +2326,7 @@
       <c r="G6" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>29669</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -2355,7 +2355,7 @@
       <c r="G7" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>29669</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -2384,7 +2384,7 @@
       <c r="G8" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>29669</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -2413,7 +2413,7 @@
       <c r="G9" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>29669</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -2442,7 +2442,7 @@
       <c r="G10" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10">
         <v>29669</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -2471,7 +2471,7 @@
       <c r="G11" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>29669</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -2500,7 +2500,7 @@
       <c r="G12" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>29669</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -2529,7 +2529,7 @@
       <c r="G13" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>29669</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -2558,7 +2558,7 @@
       <c r="G14" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14">
         <v>29669</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -2587,7 +2587,7 @@
       <c r="G15" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15">
         <v>29669</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -2616,7 +2616,7 @@
       <c r="G16" t="s">
         <v>8</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16">
         <v>29669</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -2645,7 +2645,7 @@
       <c r="G17" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17">
         <v>29669</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -2674,7 +2674,7 @@
       <c r="G18" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18">
         <v>29669</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -2703,7 +2703,7 @@
       <c r="G19" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19">
         <v>29669</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -2732,7 +2732,7 @@
       <c r="G20" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20">
         <v>29669</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -2761,7 +2761,7 @@
       <c r="G21" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21">
         <v>29669</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -2790,7 +2790,7 @@
       <c r="G22" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22">
         <v>29669</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -2819,7 +2819,7 @@
       <c r="G23" t="s">
         <v>8</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23">
         <v>29669</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -2848,7 +2848,7 @@
       <c r="G24" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24">
         <v>29669</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2877,7 +2877,7 @@
       <c r="G25" t="s">
         <v>8</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25">
         <v>29669</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -2906,7 +2906,7 @@
       <c r="G26" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26">
         <v>29669</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -2935,7 +2935,7 @@
       <c r="G27" t="s">
         <v>8</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27">
         <v>29669</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2964,7 +2964,7 @@
       <c r="G28" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28">
         <v>29669</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2993,7 +2993,7 @@
       <c r="G29" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29">
         <v>29669</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -3022,7 +3022,7 @@
       <c r="G30" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30">
         <v>29669</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -3051,7 +3051,7 @@
       <c r="G31" t="s">
         <v>8</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31">
         <v>29669</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -3080,7 +3080,7 @@
       <c r="G32" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32">
         <v>29669</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -3109,7 +3109,7 @@
       <c r="G33" t="s">
         <v>8</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33">
         <v>29669</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -3138,7 +3138,7 @@
       <c r="G34" t="s">
         <v>8</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34">
         <v>29669</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -3167,7 +3167,7 @@
       <c r="G35" t="s">
         <v>8</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35">
         <v>29669</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -3196,7 +3196,7 @@
       <c r="G36" t="s">
         <v>8</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36">
         <v>29669</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -3225,7 +3225,7 @@
       <c r="G37" t="s">
         <v>8</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37">
         <v>29669</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -3254,7 +3254,7 @@
       <c r="G38" t="s">
         <v>8</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38">
         <v>29669</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -3283,7 +3283,7 @@
       <c r="G39" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39">
         <v>29669</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -3312,7 +3312,7 @@
       <c r="G40" t="s">
         <v>8</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40">
         <v>29669</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -3341,7 +3341,7 @@
       <c r="G41" t="s">
         <v>8</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41">
         <v>29669</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -3370,7 +3370,7 @@
       <c r="G42" t="s">
         <v>8</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42">
         <v>29669</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -3399,7 +3399,7 @@
       <c r="G43" t="s">
         <v>8</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43">
         <v>29669</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -3428,7 +3428,7 @@
       <c r="G44" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H44">
         <v>29669</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -3457,7 +3457,7 @@
       <c r="G45" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H45">
         <v>29669</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -3486,7 +3486,7 @@
       <c r="G46" t="s">
         <v>8</v>
       </c>
-      <c r="H46" s="1">
+      <c r="H46">
         <v>29669</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -3515,7 +3515,7 @@
       <c r="G47" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H47">
         <v>29669</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -3544,7 +3544,7 @@
       <c r="G48" t="s">
         <v>8</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H48">
         <v>29669</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -3573,7 +3573,7 @@
       <c r="G49" t="s">
         <v>8</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H49">
         <v>29669</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -3602,7 +3602,7 @@
       <c r="G50" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H50">
         <v>29669</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -3631,7 +3631,7 @@
       <c r="G51" t="s">
         <v>8</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51">
         <v>29669</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -3660,7 +3660,7 @@
       <c r="G52" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H52">
         <v>29669</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -3689,7 +3689,7 @@
       <c r="G53" t="s">
         <v>8</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H53">
         <v>29669</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -3718,7 +3718,7 @@
       <c r="G54" t="s">
         <v>8</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H54">
         <v>29669</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -3747,7 +3747,7 @@
       <c r="G55" t="s">
         <v>8</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H55">
         <v>29669</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -3776,7 +3776,7 @@
       <c r="G56" t="s">
         <v>8</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H56">
         <v>29669</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -3805,7 +3805,7 @@
       <c r="G57" t="s">
         <v>8</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H57">
         <v>29669</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -3834,7 +3834,7 @@
       <c r="G58" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58">
         <v>29669</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -3863,7 +3863,7 @@
       <c r="G59" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59">
         <v>29669</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -3892,7 +3892,7 @@
       <c r="G60" t="s">
         <v>8</v>
       </c>
-      <c r="H60" s="1">
+      <c r="H60">
         <v>29669</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -3921,7 +3921,7 @@
       <c r="G61" t="s">
         <v>8</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H61">
         <v>29669</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -3950,7 +3950,7 @@
       <c r="G62" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="1">
+      <c r="H62">
         <v>29669</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -3979,7 +3979,7 @@
       <c r="G63" t="s">
         <v>8</v>
       </c>
-      <c r="H63" s="1">
+      <c r="H63">
         <v>29669</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -4008,7 +4008,7 @@
       <c r="G64" t="s">
         <v>8</v>
       </c>
-      <c r="H64" s="1">
+      <c r="H64">
         <v>29669</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -4037,7 +4037,7 @@
       <c r="G65" t="s">
         <v>8</v>
       </c>
-      <c r="H65" s="1">
+      <c r="H65">
         <v>29669</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -4066,7 +4066,7 @@
       <c r="G66" t="s">
         <v>8</v>
       </c>
-      <c r="H66" s="1">
+      <c r="H66">
         <v>29669</v>
       </c>
       <c r="I66" s="1" t="s">
@@ -4095,7 +4095,7 @@
       <c r="G67" t="s">
         <v>8</v>
       </c>
-      <c r="H67" s="1">
+      <c r="H67">
         <v>29669</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -4124,7 +4124,7 @@
       <c r="G68" t="s">
         <v>8</v>
       </c>
-      <c r="H68" s="1">
+      <c r="H68">
         <v>29669</v>
       </c>
       <c r="I68" s="1" t="s">
@@ -4153,7 +4153,7 @@
       <c r="G69" t="s">
         <v>8</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H69">
         <v>29669</v>
       </c>
       <c r="I69" s="1" t="s">
@@ -4182,7 +4182,7 @@
       <c r="G70" t="s">
         <v>8</v>
       </c>
-      <c r="H70" s="1">
+      <c r="H70">
         <v>29669</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -4211,7 +4211,7 @@
       <c r="G71" t="s">
         <v>8</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H71">
         <v>29669</v>
       </c>
       <c r="I71" s="1" t="s">
@@ -4240,7 +4240,7 @@
       <c r="G72" t="s">
         <v>8</v>
       </c>
-      <c r="H72" s="1">
+      <c r="H72">
         <v>29669</v>
       </c>
       <c r="I72" s="1" t="s">
@@ -4269,7 +4269,7 @@
       <c r="G73" t="s">
         <v>8</v>
       </c>
-      <c r="H73" s="1">
+      <c r="H73">
         <v>29669</v>
       </c>
       <c r="I73" s="1" t="s">
@@ -4298,7 +4298,7 @@
       <c r="G74" t="s">
         <v>8</v>
       </c>
-      <c r="H74" s="1">
+      <c r="H74">
         <v>29669</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -4327,7 +4327,7 @@
       <c r="G75" t="s">
         <v>8</v>
       </c>
-      <c r="H75" s="1">
+      <c r="H75">
         <v>29669</v>
       </c>
       <c r="I75" s="1" t="s">
@@ -4356,7 +4356,7 @@
       <c r="G76" t="s">
         <v>8</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H76">
         <v>29669</v>
       </c>
       <c r="I76" s="1" t="s">
@@ -4385,7 +4385,7 @@
       <c r="G77" t="s">
         <v>8</v>
       </c>
-      <c r="H77" s="1">
+      <c r="H77">
         <v>29669</v>
       </c>
       <c r="I77" s="1" t="s">
@@ -4414,7 +4414,7 @@
       <c r="G78" t="s">
         <v>8</v>
       </c>
-      <c r="H78" s="1">
+      <c r="H78">
         <v>29669</v>
       </c>
       <c r="I78" s="1" t="s">
@@ -4443,7 +4443,7 @@
       <c r="G79" t="s">
         <v>8</v>
       </c>
-      <c r="H79" s="1">
+      <c r="H79">
         <v>29669</v>
       </c>
       <c r="I79" s="1" t="s">
@@ -4472,7 +4472,7 @@
       <c r="G80" t="s">
         <v>8</v>
       </c>
-      <c r="H80" s="1">
+      <c r="H80">
         <v>29669</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -4501,7 +4501,7 @@
       <c r="G81" t="s">
         <v>8</v>
       </c>
-      <c r="H81" s="1">
+      <c r="H81">
         <v>29669</v>
       </c>
       <c r="I81" s="1" t="s">
@@ -4530,7 +4530,7 @@
       <c r="G82" t="s">
         <v>8</v>
       </c>
-      <c r="H82" s="1">
+      <c r="H82">
         <v>29669</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -4559,7 +4559,7 @@
       <c r="G83" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="1">
+      <c r="H83">
         <v>29669</v>
       </c>
       <c r="I83" s="1" t="s">
@@ -4588,7 +4588,7 @@
       <c r="G84" t="s">
         <v>8</v>
       </c>
-      <c r="H84" s="1">
+      <c r="H84">
         <v>29669</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -4617,7 +4617,7 @@
       <c r="G85" t="s">
         <v>8</v>
       </c>
-      <c r="H85" s="1">
+      <c r="H85">
         <v>29669</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -4646,7 +4646,7 @@
       <c r="G86" t="s">
         <v>8</v>
       </c>
-      <c r="H86" s="1">
+      <c r="H86">
         <v>29669</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -4675,7 +4675,7 @@
       <c r="G87" t="s">
         <v>8</v>
       </c>
-      <c r="H87" s="1">
+      <c r="H87">
         <v>29669</v>
       </c>
       <c r="I87" s="1" t="s">
@@ -4704,7 +4704,7 @@
       <c r="G88" t="s">
         <v>8</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H88">
         <v>29669</v>
       </c>
       <c r="I88" s="1" t="s">
@@ -4733,7 +4733,7 @@
       <c r="G89" t="s">
         <v>8</v>
       </c>
-      <c r="H89" s="1">
+      <c r="H89">
         <v>29669</v>
       </c>
       <c r="I89" s="1" t="s">
@@ -4762,7 +4762,7 @@
       <c r="G90" t="s">
         <v>8</v>
       </c>
-      <c r="H90" s="1">
+      <c r="H90">
         <v>29669</v>
       </c>
       <c r="I90" s="1" t="s">
@@ -4791,7 +4791,7 @@
       <c r="G91" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="1">
+      <c r="H91">
         <v>29669</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -4820,7 +4820,7 @@
       <c r="G92" t="s">
         <v>8</v>
       </c>
-      <c r="H92" s="1">
+      <c r="H92">
         <v>29669</v>
       </c>
       <c r="I92" s="1" t="s">
@@ -4849,7 +4849,7 @@
       <c r="G93" t="s">
         <v>8</v>
       </c>
-      <c r="H93" s="1">
+      <c r="H93">
         <v>29669</v>
       </c>
       <c r="I93" s="1" t="s">
@@ -4878,7 +4878,7 @@
       <c r="G94" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="1">
+      <c r="H94">
         <v>29669</v>
       </c>
       <c r="I94" s="1" t="s">
@@ -4907,7 +4907,7 @@
       <c r="G95" t="s">
         <v>8</v>
       </c>
-      <c r="H95" s="1">
+      <c r="H95">
         <v>29669</v>
       </c>
       <c r="I95" s="1" t="s">
@@ -4936,7 +4936,7 @@
       <c r="G96" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="1">
+      <c r="H96">
         <v>29669</v>
       </c>
       <c r="I96" s="1" t="s">
@@ -4965,7 +4965,7 @@
       <c r="G97" t="s">
         <v>8</v>
       </c>
-      <c r="H97" s="1">
+      <c r="H97">
         <v>29669</v>
       </c>
       <c r="I97" s="1" t="s">
@@ -4994,7 +4994,7 @@
       <c r="G98" t="s">
         <v>8</v>
       </c>
-      <c r="H98" s="1">
+      <c r="H98">
         <v>29669</v>
       </c>
       <c r="I98" s="1" t="s">
@@ -5023,7 +5023,7 @@
       <c r="G99" t="s">
         <v>8</v>
       </c>
-      <c r="H99" s="1">
+      <c r="H99">
         <v>29669</v>
       </c>
       <c r="I99" s="1" t="s">
@@ -5052,7 +5052,7 @@
       <c r="G100" t="s">
         <v>8</v>
       </c>
-      <c r="H100" s="1">
+      <c r="H100">
         <v>29669</v>
       </c>
       <c r="I100" s="1" t="s">
@@ -5081,7 +5081,7 @@
       <c r="G101" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="1">
+      <c r="H101">
         <v>29669</v>
       </c>
       <c r="I101" s="1" t="s">
@@ -5110,7 +5110,7 @@
       <c r="G102" t="s">
         <v>8</v>
       </c>
-      <c r="H102" s="1">
+      <c r="H102">
         <v>29669</v>
       </c>
       <c r="I102" s="1" t="s">
@@ -5139,7 +5139,7 @@
       <c r="G103" t="s">
         <v>8</v>
       </c>
-      <c r="H103" s="1">
+      <c r="H103">
         <v>29669</v>
       </c>
       <c r="I103" s="1" t="s">
@@ -5168,7 +5168,7 @@
       <c r="G104" t="s">
         <v>8</v>
       </c>
-      <c r="H104" s="1">
+      <c r="H104">
         <v>29669</v>
       </c>
       <c r="I104" s="1" t="s">
@@ -5197,7 +5197,7 @@
       <c r="G105" t="s">
         <v>8</v>
       </c>
-      <c r="H105" s="1">
+      <c r="H105">
         <v>29669</v>
       </c>
       <c r="I105" s="1" t="s">
@@ -5226,7 +5226,7 @@
       <c r="G106" t="s">
         <v>8</v>
       </c>
-      <c r="H106" s="1">
+      <c r="H106">
         <v>29669</v>
       </c>
       <c r="I106" s="1" t="s">
@@ -5255,7 +5255,7 @@
       <c r="G107" t="s">
         <v>8</v>
       </c>
-      <c r="H107" s="1">
+      <c r="H107">
         <v>29669</v>
       </c>
       <c r="I107" s="1" t="s">
@@ -5284,7 +5284,7 @@
       <c r="G108" t="s">
         <v>8</v>
       </c>
-      <c r="H108" s="1">
+      <c r="H108">
         <v>29669</v>
       </c>
       <c r="I108" s="1" t="s">
@@ -5313,7 +5313,7 @@
       <c r="G109" t="s">
         <v>8</v>
       </c>
-      <c r="H109" s="1">
+      <c r="H109">
         <v>29669</v>
       </c>
       <c r="I109" s="1" t="s">
@@ -5342,7 +5342,7 @@
       <c r="G110" t="s">
         <v>8</v>
       </c>
-      <c r="H110" s="1">
+      <c r="H110">
         <v>29669</v>
       </c>
       <c r="I110" s="1" t="s">
@@ -5371,7 +5371,7 @@
       <c r="G111" t="s">
         <v>8</v>
       </c>
-      <c r="H111" s="1">
+      <c r="H111">
         <v>29669</v>
       </c>
       <c r="I111" s="1" t="s">
@@ -5400,7 +5400,7 @@
       <c r="G112" t="s">
         <v>8</v>
       </c>
-      <c r="H112" s="1">
+      <c r="H112">
         <v>29669</v>
       </c>
       <c r="I112" s="1" t="s">
@@ -5429,7 +5429,7 @@
       <c r="G113" t="s">
         <v>8</v>
       </c>
-      <c r="H113" s="1">
+      <c r="H113">
         <v>29669</v>
       </c>
       <c r="I113" s="1" t="s">
@@ -5458,7 +5458,7 @@
       <c r="G114" t="s">
         <v>8</v>
       </c>
-      <c r="H114" s="1">
+      <c r="H114">
         <v>29669</v>
       </c>
       <c r="I114" s="1" t="s">
@@ -5487,7 +5487,7 @@
       <c r="G115" t="s">
         <v>8</v>
       </c>
-      <c r="H115" s="1">
+      <c r="H115">
         <v>29669</v>
       </c>
       <c r="I115" s="1" t="s">
@@ -5516,7 +5516,7 @@
       <c r="G116" t="s">
         <v>8</v>
       </c>
-      <c r="H116" s="1">
+      <c r="H116">
         <v>29669</v>
       </c>
       <c r="I116" s="1" t="s">
@@ -5545,7 +5545,7 @@
       <c r="G117" t="s">
         <v>8</v>
       </c>
-      <c r="H117" s="1">
+      <c r="H117">
         <v>29669</v>
       </c>
       <c r="I117" s="1" t="s">
@@ -5574,7 +5574,7 @@
       <c r="G118" t="s">
         <v>8</v>
       </c>
-      <c r="H118" s="1">
+      <c r="H118">
         <v>29669</v>
       </c>
       <c r="I118" s="1" t="s">
@@ -5603,7 +5603,7 @@
       <c r="G119" t="s">
         <v>8</v>
       </c>
-      <c r="H119" s="1">
+      <c r="H119">
         <v>29669</v>
       </c>
       <c r="I119" s="1" t="s">
@@ -5632,7 +5632,7 @@
       <c r="G120" t="s">
         <v>8</v>
       </c>
-      <c r="H120" s="1">
+      <c r="H120">
         <v>29669</v>
       </c>
       <c r="I120" s="1" t="s">
@@ -5661,7 +5661,7 @@
       <c r="G121" t="s">
         <v>8</v>
       </c>
-      <c r="H121" s="1">
+      <c r="H121">
         <v>29669</v>
       </c>
       <c r="I121" s="1" t="s">
@@ -5690,7 +5690,7 @@
       <c r="G122" t="s">
         <v>8</v>
       </c>
-      <c r="H122" s="1">
+      <c r="H122">
         <v>29669</v>
       </c>
       <c r="I122" s="1" t="s">
@@ -5719,7 +5719,7 @@
       <c r="G123" t="s">
         <v>8</v>
       </c>
-      <c r="H123" s="1">
+      <c r="H123">
         <v>29669</v>
       </c>
       <c r="I123" s="1" t="s">
@@ -5748,7 +5748,7 @@
       <c r="G124" t="s">
         <v>8</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H124">
         <v>29669</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -5777,7 +5777,7 @@
       <c r="G125" t="s">
         <v>8</v>
       </c>
-      <c r="H125" s="1">
+      <c r="H125">
         <v>29669</v>
       </c>
       <c r="I125" s="1" t="s">
@@ -5806,7 +5806,7 @@
       <c r="G126" t="s">
         <v>8</v>
       </c>
-      <c r="H126" s="1">
+      <c r="H126">
         <v>29669</v>
       </c>
       <c r="I126" s="1" t="s">
@@ -5835,7 +5835,7 @@
       <c r="G127" t="s">
         <v>8</v>
       </c>
-      <c r="H127" s="1">
+      <c r="H127">
         <v>29669</v>
       </c>
       <c r="I127" s="1" t="s">
@@ -5864,7 +5864,7 @@
       <c r="G128" t="s">
         <v>8</v>
       </c>
-      <c r="H128" s="1">
+      <c r="H128">
         <v>29669</v>
       </c>
       <c r="I128" s="1" t="s">
@@ -5893,7 +5893,7 @@
       <c r="G129" t="s">
         <v>8</v>
       </c>
-      <c r="H129" s="1">
+      <c r="H129">
         <v>29669</v>
       </c>
       <c r="I129" s="1" t="s">
@@ -5922,7 +5922,7 @@
       <c r="G130" t="s">
         <v>8</v>
       </c>
-      <c r="H130" s="1">
+      <c r="H130">
         <v>29669</v>
       </c>
       <c r="I130" s="1" t="s">
@@ -5951,7 +5951,7 @@
       <c r="G131" t="s">
         <v>8</v>
       </c>
-      <c r="H131" s="1">
+      <c r="H131">
         <v>29669</v>
       </c>
       <c r="I131" s="1" t="s">
@@ -5980,7 +5980,7 @@
       <c r="G132" t="s">
         <v>8</v>
       </c>
-      <c r="H132" s="1">
+      <c r="H132">
         <v>29669</v>
       </c>
       <c r="I132" s="1" t="s">
@@ -6009,7 +6009,7 @@
       <c r="G133" t="s">
         <v>8</v>
       </c>
-      <c r="H133" s="1">
+      <c r="H133">
         <v>29669</v>
       </c>
       <c r="I133" s="1" t="s">
@@ -6038,7 +6038,7 @@
       <c r="G134" t="s">
         <v>8</v>
       </c>
-      <c r="H134" s="1">
+      <c r="H134">
         <v>29669</v>
       </c>
       <c r="I134" s="1" t="s">
@@ -6067,7 +6067,7 @@
       <c r="G135" t="s">
         <v>8</v>
       </c>
-      <c r="H135" s="1">
+      <c r="H135">
         <v>29669</v>
       </c>
       <c r="I135" s="1" t="s">
@@ -6096,7 +6096,7 @@
       <c r="G136" t="s">
         <v>8</v>
       </c>
-      <c r="H136" s="1">
+      <c r="H136">
         <v>29669</v>
       </c>
       <c r="I136" s="1" t="s">
@@ -6125,7 +6125,7 @@
       <c r="G137" t="s">
         <v>8</v>
       </c>
-      <c r="H137" s="1">
+      <c r="H137">
         <v>29669</v>
       </c>
       <c r="I137" s="1" t="s">
@@ -6154,7 +6154,7 @@
       <c r="G138" t="s">
         <v>8</v>
       </c>
-      <c r="H138" s="1">
+      <c r="H138">
         <v>29669</v>
       </c>
       <c r="I138" s="1" t="s">
@@ -6183,7 +6183,7 @@
       <c r="G139" t="s">
         <v>8</v>
       </c>
-      <c r="H139" s="1">
+      <c r="H139">
         <v>29669</v>
       </c>
       <c r="I139" s="1" t="s">
@@ -6212,7 +6212,7 @@
       <c r="G140" t="s">
         <v>8</v>
       </c>
-      <c r="H140" s="1">
+      <c r="H140">
         <v>29669</v>
       </c>
       <c r="I140" s="1" t="s">
@@ -6241,7 +6241,7 @@
       <c r="G141" t="s">
         <v>8</v>
       </c>
-      <c r="H141" s="1">
+      <c r="H141">
         <v>29669</v>
       </c>
       <c r="I141" s="1" t="s">
@@ -6270,7 +6270,7 @@
       <c r="G142" t="s">
         <v>8</v>
       </c>
-      <c r="H142" s="1">
+      <c r="H142">
         <v>29669</v>
       </c>
       <c r="I142" s="1" t="s">
@@ -6299,7 +6299,7 @@
       <c r="G143" t="s">
         <v>8</v>
       </c>
-      <c r="H143" s="1">
+      <c r="H143">
         <v>29669</v>
       </c>
       <c r="I143" s="1" t="s">
@@ -6328,7 +6328,7 @@
       <c r="G144" t="s">
         <v>8</v>
       </c>
-      <c r="H144" s="1">
+      <c r="H144">
         <v>29669</v>
       </c>
       <c r="I144" s="1" t="s">
@@ -6357,7 +6357,7 @@
       <c r="G145" t="s">
         <v>8</v>
       </c>
-      <c r="H145" s="1">
+      <c r="H145">
         <v>29669</v>
       </c>
       <c r="I145" s="1" t="s">
@@ -6386,7 +6386,7 @@
       <c r="G146" t="s">
         <v>8</v>
       </c>
-      <c r="H146" s="1">
+      <c r="H146">
         <v>29669</v>
       </c>
       <c r="I146" s="1" t="s">
@@ -6415,7 +6415,7 @@
       <c r="G147" t="s">
         <v>8</v>
       </c>
-      <c r="H147" s="1">
+      <c r="H147">
         <v>29669</v>
       </c>
       <c r="I147" s="1" t="s">
@@ -6444,7 +6444,7 @@
       <c r="G148" t="s">
         <v>8</v>
       </c>
-      <c r="H148" s="1">
+      <c r="H148">
         <v>29669</v>
       </c>
       <c r="I148" s="1" t="s">
@@ -6473,7 +6473,7 @@
       <c r="G149" t="s">
         <v>8</v>
       </c>
-      <c r="H149" s="1">
+      <c r="H149">
         <v>29669</v>
       </c>
       <c r="I149" s="1" t="s">
@@ -6502,7 +6502,7 @@
       <c r="G150" t="s">
         <v>8</v>
       </c>
-      <c r="H150" s="1">
+      <c r="H150">
         <v>29669</v>
       </c>
       <c r="I150" s="1" t="s">
@@ -6531,7 +6531,7 @@
       <c r="G151" t="s">
         <v>8</v>
       </c>
-      <c r="H151" s="1">
+      <c r="H151">
         <v>29669</v>
       </c>
       <c r="I151" s="1" t="s">
@@ -6560,7 +6560,7 @@
       <c r="G152" t="s">
         <v>8</v>
       </c>
-      <c r="H152" s="1">
+      <c r="H152">
         <v>29669</v>
       </c>
       <c r="I152" s="1" t="s">
@@ -6589,7 +6589,7 @@
       <c r="G153" t="s">
         <v>8</v>
       </c>
-      <c r="H153" s="1">
+      <c r="H153">
         <v>29669</v>
       </c>
       <c r="I153" s="1" t="s">
@@ -6618,7 +6618,7 @@
       <c r="G154" t="s">
         <v>8</v>
       </c>
-      <c r="H154" s="1">
+      <c r="H154">
         <v>29669</v>
       </c>
       <c r="I154" s="1" t="s">
@@ -6647,7 +6647,7 @@
       <c r="G155" t="s">
         <v>8</v>
       </c>
-      <c r="H155" s="1">
+      <c r="H155">
         <v>29669</v>
       </c>
       <c r="I155" s="1" t="s">
@@ -6676,7 +6676,7 @@
       <c r="G156" t="s">
         <v>8</v>
       </c>
-      <c r="H156" s="1">
+      <c r="H156">
         <v>29669</v>
       </c>
       <c r="I156" s="1" t="s">
@@ -6705,7 +6705,7 @@
       <c r="G157" t="s">
         <v>8</v>
       </c>
-      <c r="H157" s="1">
+      <c r="H157">
         <v>29669</v>
       </c>
       <c r="I157" s="1" t="s">
@@ -6734,7 +6734,7 @@
       <c r="G158" t="s">
         <v>8</v>
       </c>
-      <c r="H158" s="1">
+      <c r="H158">
         <v>29669</v>
       </c>
       <c r="I158" s="1" t="s">
@@ -6763,7 +6763,7 @@
       <c r="G159" t="s">
         <v>8</v>
       </c>
-      <c r="H159" s="1">
+      <c r="H159">
         <v>29669</v>
       </c>
       <c r="I159" s="1" t="s">
@@ -6792,7 +6792,7 @@
       <c r="G160" t="s">
         <v>8</v>
       </c>
-      <c r="H160" s="1">
+      <c r="H160">
         <v>29669</v>
       </c>
       <c r="I160" s="1" t="s">
@@ -6821,7 +6821,7 @@
       <c r="G161" t="s">
         <v>8</v>
       </c>
-      <c r="H161" s="1">
+      <c r="H161">
         <v>29669</v>
       </c>
       <c r="I161" s="1" t="s">
@@ -6850,7 +6850,7 @@
       <c r="G162" t="s">
         <v>8</v>
       </c>
-      <c r="H162" s="1">
+      <c r="H162">
         <v>29669</v>
       </c>
       <c r="I162" s="1" t="s">
@@ -6879,7 +6879,7 @@
       <c r="G163" t="s">
         <v>8</v>
       </c>
-      <c r="H163" s="1">
+      <c r="H163">
         <v>29669</v>
       </c>
       <c r="I163" s="1" t="s">
@@ -6908,7 +6908,7 @@
       <c r="G164" t="s">
         <v>8</v>
       </c>
-      <c r="H164" s="1">
+      <c r="H164">
         <v>29669</v>
       </c>
       <c r="I164" s="1" t="s">
@@ -6937,7 +6937,7 @@
       <c r="G165" t="s">
         <v>8</v>
       </c>
-      <c r="H165" s="1">
+      <c r="H165">
         <v>29669</v>
       </c>
       <c r="I165" s="1" t="s">
@@ -6966,7 +6966,7 @@
       <c r="G166" t="s">
         <v>8</v>
       </c>
-      <c r="H166" s="1">
+      <c r="H166">
         <v>29669</v>
       </c>
       <c r="I166" s="1" t="s">
@@ -6995,7 +6995,7 @@
       <c r="G167" t="s">
         <v>8</v>
       </c>
-      <c r="H167" s="1">
+      <c r="H167">
         <v>29669</v>
       </c>
       <c r="I167" s="1" t="s">
@@ -7024,7 +7024,7 @@
       <c r="G168" t="s">
         <v>8</v>
       </c>
-      <c r="H168" s="1">
+      <c r="H168">
         <v>29669</v>
       </c>
       <c r="I168" s="1" t="s">
@@ -7053,7 +7053,7 @@
       <c r="G169" t="s">
         <v>8</v>
       </c>
-      <c r="H169" s="1">
+      <c r="H169">
         <v>29669</v>
       </c>
       <c r="I169" s="1" t="s">
@@ -7082,7 +7082,7 @@
       <c r="G170" t="s">
         <v>8</v>
       </c>
-      <c r="H170" s="1">
+      <c r="H170">
         <v>29669</v>
       </c>
       <c r="I170" s="1" t="s">
@@ -7111,7 +7111,7 @@
       <c r="G171" t="s">
         <v>8</v>
       </c>
-      <c r="H171" s="1">
+      <c r="H171">
         <v>29669</v>
       </c>
       <c r="I171" s="1" t="s">
@@ -7140,7 +7140,7 @@
       <c r="G172" t="s">
         <v>8</v>
       </c>
-      <c r="H172" s="1">
+      <c r="H172">
         <v>29669</v>
       </c>
       <c r="I172" s="1" t="s">
@@ -7169,7 +7169,7 @@
       <c r="G173" t="s">
         <v>8</v>
       </c>
-      <c r="H173" s="1">
+      <c r="H173">
         <v>29669</v>
       </c>
       <c r="I173" s="1" t="s">
@@ -7198,7 +7198,7 @@
       <c r="G174" t="s">
         <v>8</v>
       </c>
-      <c r="H174" s="1">
+      <c r="H174">
         <v>29669</v>
       </c>
       <c r="I174" s="1" t="s">
@@ -7227,7 +7227,7 @@
       <c r="G175" t="s">
         <v>8</v>
       </c>
-      <c r="H175" s="1">
+      <c r="H175">
         <v>29669</v>
       </c>
       <c r="I175" s="1" t="s">
@@ -7256,7 +7256,7 @@
       <c r="G176" t="s">
         <v>8</v>
       </c>
-      <c r="H176" s="1">
+      <c r="H176">
         <v>29669</v>
       </c>
       <c r="I176" s="1" t="s">
@@ -7285,7 +7285,7 @@
       <c r="G177" t="s">
         <v>8</v>
       </c>
-      <c r="H177" s="1">
+      <c r="H177">
         <v>29669</v>
       </c>
       <c r="I177" s="1" t="s">
@@ -7314,7 +7314,7 @@
       <c r="G178" t="s">
         <v>8</v>
       </c>
-      <c r="H178" s="1">
+      <c r="H178">
         <v>29669</v>
       </c>
       <c r="I178" s="1" t="s">
@@ -7343,7 +7343,7 @@
       <c r="G179" t="s">
         <v>8</v>
       </c>
-      <c r="H179" s="1">
+      <c r="H179">
         <v>29669</v>
       </c>
       <c r="I179" s="1" t="s">
@@ -7372,7 +7372,7 @@
       <c r="G180" t="s">
         <v>8</v>
       </c>
-      <c r="H180" s="1">
+      <c r="H180">
         <v>29669</v>
       </c>
       <c r="I180" s="1" t="s">
@@ -7401,7 +7401,7 @@
       <c r="G181" t="s">
         <v>8</v>
       </c>
-      <c r="H181" s="1">
+      <c r="H181">
         <v>29669</v>
       </c>
       <c r="I181" s="1" t="s">
@@ -7430,7 +7430,7 @@
       <c r="G182" t="s">
         <v>8</v>
       </c>
-      <c r="H182" s="1">
+      <c r="H182">
         <v>29669</v>
       </c>
       <c r="I182" s="1" t="s">
@@ -7459,7 +7459,7 @@
       <c r="G183" t="s">
         <v>8</v>
       </c>
-      <c r="H183" s="1">
+      <c r="H183">
         <v>29669</v>
       </c>
       <c r="I183" s="1" t="s">
@@ -7488,7 +7488,7 @@
       <c r="G184" t="s">
         <v>8</v>
       </c>
-      <c r="H184" s="1">
+      <c r="H184">
         <v>29669</v>
       </c>
       <c r="I184" s="1" t="s">
@@ -7517,7 +7517,7 @@
       <c r="G185" t="s">
         <v>8</v>
       </c>
-      <c r="H185" s="1">
+      <c r="H185">
         <v>29669</v>
       </c>
       <c r="I185" s="1" t="s">
@@ -7546,7 +7546,7 @@
       <c r="G186" t="s">
         <v>8</v>
       </c>
-      <c r="H186" s="1">
+      <c r="H186">
         <v>29669</v>
       </c>
       <c r="I186" s="1" t="s">
@@ -7575,7 +7575,7 @@
       <c r="G187" t="s">
         <v>8</v>
       </c>
-      <c r="H187" s="1">
+      <c r="H187">
         <v>29669</v>
       </c>
       <c r="I187" s="1" t="s">
@@ -7604,7 +7604,7 @@
       <c r="G188" t="s">
         <v>8</v>
       </c>
-      <c r="H188" s="1">
+      <c r="H188">
         <v>29669</v>
       </c>
       <c r="I188" s="1" t="s">
@@ -7633,7 +7633,7 @@
       <c r="G189" t="s">
         <v>8</v>
       </c>
-      <c r="H189" s="1">
+      <c r="H189">
         <v>29669</v>
       </c>
       <c r="I189" s="1" t="s">
@@ -7662,7 +7662,7 @@
       <c r="G190" t="s">
         <v>8</v>
       </c>
-      <c r="H190" s="1">
+      <c r="H190">
         <v>29669</v>
       </c>
       <c r="I190" s="1" t="s">
@@ -7691,7 +7691,7 @@
       <c r="G191" t="s">
         <v>8</v>
       </c>
-      <c r="H191" s="1">
+      <c r="H191">
         <v>29669</v>
       </c>
       <c r="I191" s="1" t="s">
@@ -7720,7 +7720,7 @@
       <c r="G192" t="s">
         <v>8</v>
       </c>
-      <c r="H192" s="1">
+      <c r="H192">
         <v>29669</v>
       </c>
       <c r="I192" s="1" t="s">
@@ -7749,7 +7749,7 @@
       <c r="G193" t="s">
         <v>8</v>
       </c>
-      <c r="H193" s="1">
+      <c r="H193">
         <v>29669</v>
       </c>
       <c r="I193" s="1" t="s">
@@ -7778,7 +7778,7 @@
       <c r="G194" t="s">
         <v>8</v>
       </c>
-      <c r="H194" s="1">
+      <c r="H194">
         <v>29669</v>
       </c>
       <c r="I194" s="1" t="s">
@@ -7807,7 +7807,7 @@
       <c r="G195" t="s">
         <v>8</v>
       </c>
-      <c r="H195" s="1">
+      <c r="H195">
         <v>29669</v>
       </c>
       <c r="I195" s="1" t="s">
@@ -7836,7 +7836,7 @@
       <c r="G196" t="s">
         <v>8</v>
       </c>
-      <c r="H196" s="1">
+      <c r="H196">
         <v>29669</v>
       </c>
       <c r="I196" s="1" t="s">
@@ -7865,7 +7865,7 @@
       <c r="G197" t="s">
         <v>8</v>
       </c>
-      <c r="H197" s="1">
+      <c r="H197">
         <v>29669</v>
       </c>
       <c r="I197" s="1" t="s">
@@ -7894,7 +7894,7 @@
       <c r="G198" t="s">
         <v>8</v>
       </c>
-      <c r="H198" s="1">
+      <c r="H198">
         <v>29669</v>
       </c>
       <c r="I198" s="1" t="s">
@@ -7923,7 +7923,7 @@
       <c r="G199" t="s">
         <v>8</v>
       </c>
-      <c r="H199" s="1">
+      <c r="H199">
         <v>29669</v>
       </c>
       <c r="I199" s="1" t="s">
@@ -7952,7 +7952,7 @@
       <c r="G200" t="s">
         <v>8</v>
       </c>
-      <c r="H200" s="1">
+      <c r="H200">
         <v>29669</v>
       </c>
       <c r="I200" s="1" t="s">
@@ -7981,7 +7981,7 @@
       <c r="G201" t="s">
         <v>8</v>
       </c>
-      <c r="H201" s="1">
+      <c r="H201">
         <v>29669</v>
       </c>
       <c r="I201" s="1" t="s">
@@ -8010,7 +8010,7 @@
       <c r="G202" t="s">
         <v>8</v>
       </c>
-      <c r="H202" s="1">
+      <c r="H202">
         <v>29669</v>
       </c>
       <c r="I202" s="1" t="s">
@@ -8039,7 +8039,7 @@
       <c r="G203" t="s">
         <v>8</v>
       </c>
-      <c r="H203" s="1">
+      <c r="H203">
         <v>29669</v>
       </c>
       <c r="I203" s="1" t="s">
@@ -8068,7 +8068,7 @@
       <c r="G204" t="s">
         <v>8</v>
       </c>
-      <c r="H204" s="1">
+      <c r="H204">
         <v>29669</v>
       </c>
       <c r="I204" s="1" t="s">
@@ -8097,7 +8097,7 @@
       <c r="G205" t="s">
         <v>8</v>
       </c>
-      <c r="H205" s="1">
+      <c r="H205">
         <v>29669</v>
       </c>
       <c r="I205" s="1" t="s">
@@ -8126,7 +8126,7 @@
       <c r="G206" t="s">
         <v>8</v>
       </c>
-      <c r="H206" s="1">
+      <c r="H206">
         <v>29669</v>
       </c>
       <c r="I206" s="1" t="s">
@@ -8155,7 +8155,7 @@
       <c r="G207" t="s">
         <v>8</v>
       </c>
-      <c r="H207" s="1">
+      <c r="H207">
         <v>29669</v>
       </c>
       <c r="I207" s="1" t="s">
@@ -8184,7 +8184,7 @@
       <c r="G208" t="s">
         <v>8</v>
       </c>
-      <c r="H208" s="1">
+      <c r="H208">
         <v>29669</v>
       </c>
       <c r="I208" s="1" t="s">
@@ -8213,7 +8213,7 @@
       <c r="G209" t="s">
         <v>8</v>
       </c>
-      <c r="H209" s="1">
+      <c r="H209">
         <v>29669</v>
       </c>
       <c r="I209" s="1" t="s">
@@ -8242,7 +8242,7 @@
       <c r="G210" t="s">
         <v>8</v>
       </c>
-      <c r="H210" s="1">
+      <c r="H210">
         <v>29669</v>
       </c>
       <c r="I210" s="1" t="s">
@@ -8271,7 +8271,7 @@
       <c r="G211" t="s">
         <v>8</v>
       </c>
-      <c r="H211" s="1">
+      <c r="H211">
         <v>29669</v>
       </c>
       <c r="I211" s="1" t="s">
@@ -8300,7 +8300,7 @@
       <c r="G212" t="s">
         <v>8</v>
       </c>
-      <c r="H212" s="1">
+      <c r="H212">
         <v>29669</v>
       </c>
       <c r="I212" s="1" t="s">
@@ -8329,7 +8329,7 @@
       <c r="G213" t="s">
         <v>8</v>
       </c>
-      <c r="H213" s="1">
+      <c r="H213">
         <v>29669</v>
       </c>
       <c r="I213" s="1" t="s">
@@ -8358,7 +8358,7 @@
       <c r="G214" t="s">
         <v>8</v>
       </c>
-      <c r="H214" s="1">
+      <c r="H214">
         <v>29669</v>
       </c>
       <c r="I214" s="1" t="s">
@@ -8387,7 +8387,7 @@
       <c r="G215" t="s">
         <v>8</v>
       </c>
-      <c r="H215" s="1">
+      <c r="H215">
         <v>29669</v>
       </c>
       <c r="I215" s="1" t="s">
@@ -8416,7 +8416,7 @@
       <c r="G216" t="s">
         <v>8</v>
       </c>
-      <c r="H216" s="1">
+      <c r="H216">
         <v>29669</v>
       </c>
       <c r="I216" s="1" t="s">
@@ -8445,7 +8445,7 @@
       <c r="G217" t="s">
         <v>8</v>
       </c>
-      <c r="H217" s="1">
+      <c r="H217">
         <v>29669</v>
       </c>
       <c r="I217" s="1" t="s">
@@ -8474,7 +8474,7 @@
       <c r="G218" t="s">
         <v>8</v>
       </c>
-      <c r="H218" s="1">
+      <c r="H218">
         <v>29669</v>
       </c>
       <c r="I218" s="1" t="s">
@@ -8503,7 +8503,7 @@
       <c r="G219" t="s">
         <v>8</v>
       </c>
-      <c r="H219" s="1">
+      <c r="H219">
         <v>29669</v>
       </c>
       <c r="I219" s="1" t="s">
@@ -8532,7 +8532,7 @@
       <c r="G220" t="s">
         <v>8</v>
       </c>
-      <c r="H220" s="1">
+      <c r="H220">
         <v>29669</v>
       </c>
       <c r="I220" s="1" t="s">
@@ -8561,7 +8561,7 @@
       <c r="G221" t="s">
         <v>8</v>
       </c>
-      <c r="H221" s="1">
+      <c r="H221">
         <v>29669</v>
       </c>
       <c r="I221" s="1" t="s">
@@ -8590,7 +8590,7 @@
       <c r="G222" t="s">
         <v>281</v>
       </c>
-      <c r="H222" s="1">
+      <c r="H222">
         <v>29669</v>
       </c>
       <c r="I222" s="1" t="s">
@@ -8619,7 +8619,7 @@
       <c r="G223" t="s">
         <v>270</v>
       </c>
-      <c r="H223" s="1">
+      <c r="H223">
         <v>29669</v>
       </c>
       <c r="I223" s="1" t="s">
@@ -8648,7 +8648,7 @@
       <c r="G224" t="s">
         <v>270</v>
       </c>
-      <c r="H224" s="1">
+      <c r="H224">
         <v>29669</v>
       </c>
       <c r="I224" s="1" t="s">
@@ -8677,7 +8677,7 @@
       <c r="G225" t="s">
         <v>281</v>
       </c>
-      <c r="H225" s="1">
+      <c r="H225">
         <v>29669</v>
       </c>
       <c r="I225" s="1" t="s">
@@ -8706,7 +8706,7 @@
       <c r="G226" t="s">
         <v>281</v>
       </c>
-      <c r="H226" s="1">
+      <c r="H226">
         <v>29669</v>
       </c>
       <c r="I226" s="1" t="s">
@@ -8735,7 +8735,7 @@
       <c r="G227" t="s">
         <v>281</v>
       </c>
-      <c r="H227" s="1">
+      <c r="H227">
         <v>29669</v>
       </c>
       <c r="I227" s="1" t="s">
@@ -8764,7 +8764,7 @@
       <c r="G228" t="s">
         <v>281</v>
       </c>
-      <c r="H228" s="1">
+      <c r="H228">
         <v>29669</v>
       </c>
       <c r="I228" s="1" t="s">
@@ -8793,7 +8793,7 @@
       <c r="G229" t="s">
         <v>281</v>
       </c>
-      <c r="H229" s="1">
+      <c r="H229">
         <v>29669</v>
       </c>
       <c r="I229" s="1" t="s">
@@ -8822,7 +8822,7 @@
       <c r="G230" t="s">
         <v>281</v>
       </c>
-      <c r="H230" s="1">
+      <c r="H230">
         <v>29669</v>
       </c>
       <c r="I230" s="1" t="s">
@@ -8851,7 +8851,7 @@
       <c r="G231" t="s">
         <v>281</v>
       </c>
-      <c r="H231" s="1">
+      <c r="H231">
         <v>29669</v>
       </c>
       <c r="I231" s="1" t="s">
@@ -8880,7 +8880,7 @@
       <c r="G232" t="s">
         <v>281</v>
       </c>
-      <c r="H232" s="1">
+      <c r="H232">
         <v>29669</v>
       </c>
       <c r="I232" s="1" t="s">
@@ -8909,7 +8909,7 @@
       <c r="G233" t="s">
         <v>8</v>
       </c>
-      <c r="H233" s="1">
+      <c r="H233">
         <v>29669</v>
       </c>
       <c r="I233" s="1" t="s">
@@ -8938,7 +8938,7 @@
       <c r="G234" t="s">
         <v>8</v>
       </c>
-      <c r="H234" s="1">
+      <c r="H234">
         <v>29669</v>
       </c>
       <c r="I234" s="1" t="s">
@@ -8967,7 +8967,7 @@
       <c r="G235" t="s">
         <v>8</v>
       </c>
-      <c r="H235" s="1">
+      <c r="H235">
         <v>29669</v>
       </c>
       <c r="I235" s="1" t="s">
@@ -8996,7 +8996,7 @@
       <c r="G236" t="s">
         <v>8</v>
       </c>
-      <c r="H236" s="1">
+      <c r="H236">
         <v>29669</v>
       </c>
       <c r="I236" s="1" t="s">
@@ -9025,7 +9025,7 @@
       <c r="G237" t="s">
         <v>8</v>
       </c>
-      <c r="H237" s="1">
+      <c r="H237">
         <v>29669</v>
       </c>
       <c r="I237" s="1" t="s">
@@ -9054,7 +9054,7 @@
       <c r="G238" t="s">
         <v>8</v>
       </c>
-      <c r="H238" s="1">
+      <c r="H238">
         <v>29669</v>
       </c>
       <c r="I238" s="1" t="s">
@@ -9083,7 +9083,7 @@
       <c r="G239" t="s">
         <v>8</v>
       </c>
-      <c r="H239" s="1">
+      <c r="H239">
         <v>29669</v>
       </c>
       <c r="I239" s="1" t="s">
@@ -9112,7 +9112,7 @@
       <c r="G240" t="s">
         <v>8</v>
       </c>
-      <c r="H240" s="1">
+      <c r="H240">
         <v>29669</v>
       </c>
       <c r="I240" s="1" t="s">
@@ -9141,7 +9141,7 @@
       <c r="G241" t="s">
         <v>8</v>
       </c>
-      <c r="H241" s="1">
+      <c r="H241">
         <v>29669</v>
       </c>
       <c r="I241" s="1" t="s">
@@ -9170,7 +9170,7 @@
       <c r="G242" t="s">
         <v>8</v>
       </c>
-      <c r="H242" s="1">
+      <c r="H242">
         <v>29669</v>
       </c>
       <c r="I242" s="1" t="s">
@@ -9199,7 +9199,7 @@
       <c r="G243" t="s">
         <v>8</v>
       </c>
-      <c r="H243" s="1">
+      <c r="H243">
         <v>29669</v>
       </c>
       <c r="I243" s="1" t="s">
@@ -9228,7 +9228,7 @@
       <c r="G244" t="s">
         <v>281</v>
       </c>
-      <c r="H244" s="1">
+      <c r="H244">
         <v>29669</v>
       </c>
       <c r="I244" s="1" t="s">
@@ -9257,7 +9257,7 @@
       <c r="G245" t="s">
         <v>8</v>
       </c>
-      <c r="H245" s="1">
+      <c r="H245">
         <v>29669</v>
       </c>
       <c r="I245" s="1" t="s">
@@ -9286,7 +9286,7 @@
       <c r="G246" t="s">
         <v>8</v>
       </c>
-      <c r="H246" s="1">
+      <c r="H246">
         <v>29669</v>
       </c>
       <c r="I246" s="1" t="s">
@@ -9315,7 +9315,7 @@
       <c r="G247" t="s">
         <v>8</v>
       </c>
-      <c r="H247" s="1">
+      <c r="H247">
         <v>29669</v>
       </c>
       <c r="I247" s="1" t="s">
@@ -9344,7 +9344,7 @@
       <c r="G248" t="s">
         <v>8</v>
       </c>
-      <c r="H248" s="1">
+      <c r="H248">
         <v>29669</v>
       </c>
       <c r="I248" s="1" t="s">
@@ -9373,7 +9373,7 @@
       <c r="G249" t="s">
         <v>8</v>
       </c>
-      <c r="H249" s="1">
+      <c r="H249">
         <v>29669</v>
       </c>
       <c r="I249" s="1" t="s">
@@ -9402,7 +9402,7 @@
       <c r="G250" t="s">
         <v>8</v>
       </c>
-      <c r="H250" s="1">
+      <c r="H250">
         <v>29669</v>
       </c>
       <c r="I250" s="1" t="s">
@@ -9431,7 +9431,7 @@
       <c r="G251" t="s">
         <v>8</v>
       </c>
-      <c r="H251" s="1">
+      <c r="H251">
         <v>29669</v>
       </c>
       <c r="I251" s="1" t="s">
@@ -9460,7 +9460,7 @@
       <c r="G252" t="s">
         <v>8</v>
       </c>
-      <c r="H252" s="1">
+      <c r="H252">
         <v>29669</v>
       </c>
       <c r="I252" s="1" t="s">
@@ -9489,7 +9489,7 @@
       <c r="G253" t="s">
         <v>8</v>
       </c>
-      <c r="H253" s="1">
+      <c r="H253">
         <v>29669</v>
       </c>
       <c r="I253" s="1" t="s">
@@ -9518,7 +9518,7 @@
       <c r="G254" t="s">
         <v>8</v>
       </c>
-      <c r="H254" s="1">
+      <c r="H254">
         <v>29669</v>
       </c>
       <c r="I254" s="1" t="s">
@@ -9547,7 +9547,7 @@
       <c r="G255" t="s">
         <v>8</v>
       </c>
-      <c r="H255" s="1">
+      <c r="H255">
         <v>29669</v>
       </c>
       <c r="I255" s="1" t="s">
@@ -9576,7 +9576,7 @@
       <c r="G256" t="s">
         <v>8</v>
       </c>
-      <c r="H256" s="1">
+      <c r="H256">
         <v>29669</v>
       </c>
       <c r="I256" s="1" t="s">
@@ -9605,7 +9605,7 @@
       <c r="G257" t="s">
         <v>8</v>
       </c>
-      <c r="H257" s="1">
+      <c r="H257">
         <v>29669</v>
       </c>
       <c r="I257" s="1" t="s">
@@ -9634,7 +9634,7 @@
       <c r="G258" t="s">
         <v>8</v>
       </c>
-      <c r="H258" s="1">
+      <c r="H258">
         <v>29669</v>
       </c>
       <c r="I258" s="1" t="s">
@@ -9663,7 +9663,7 @@
       <c r="G259" t="s">
         <v>8</v>
       </c>
-      <c r="H259" s="1">
+      <c r="H259">
         <v>29669</v>
       </c>
       <c r="I259" s="1" t="s">
@@ -9692,7 +9692,7 @@
       <c r="G260" t="s">
         <v>8</v>
       </c>
-      <c r="H260" s="1">
+      <c r="H260">
         <v>29669</v>
       </c>
       <c r="I260" s="1" t="s">
@@ -9721,7 +9721,7 @@
       <c r="G261" t="s">
         <v>8</v>
       </c>
-      <c r="H261" s="1">
+      <c r="H261">
         <v>29669</v>
       </c>
       <c r="I261" s="1" t="s">
@@ -9750,7 +9750,7 @@
       <c r="G262" t="s">
         <v>8</v>
       </c>
-      <c r="H262" s="1">
+      <c r="H262">
         <v>29669</v>
       </c>
       <c r="I262" s="1" t="s">
@@ -9779,7 +9779,7 @@
       <c r="G263" t="s">
         <v>8</v>
       </c>
-      <c r="H263" s="1">
+      <c r="H263">
         <v>29669</v>
       </c>
       <c r="I263" s="1" t="s">
@@ -9808,7 +9808,7 @@
       <c r="G264" t="s">
         <v>8</v>
       </c>
-      <c r="H264" s="1">
+      <c r="H264">
         <v>29669</v>
       </c>
       <c r="I264" s="1" t="s">
@@ -9837,7 +9837,7 @@
       <c r="G265" t="s">
         <v>8</v>
       </c>
-      <c r="H265" s="1">
+      <c r="H265">
         <v>29669</v>
       </c>
       <c r="I265" s="1" t="s">
@@ -9866,7 +9866,7 @@
       <c r="G266" t="s">
         <v>8</v>
       </c>
-      <c r="H266" s="1">
+      <c r="H266">
         <v>29669</v>
       </c>
       <c r="I266" s="1" t="s">
@@ -9895,7 +9895,7 @@
       <c r="G267" t="s">
         <v>8</v>
       </c>
-      <c r="H267" s="1">
+      <c r="H267">
         <v>29669</v>
       </c>
       <c r="I267" s="1" t="s">
@@ -9924,7 +9924,7 @@
       <c r="G268" t="s">
         <v>8</v>
       </c>
-      <c r="H268" s="1">
+      <c r="H268">
         <v>29669</v>
       </c>
       <c r="I268" s="1" t="s">
@@ -9953,7 +9953,7 @@
       <c r="G269" t="s">
         <v>8</v>
       </c>
-      <c r="H269" s="1">
+      <c r="H269">
         <v>29669</v>
       </c>
       <c r="I269" s="1" t="s">
@@ -9982,7 +9982,7 @@
       <c r="G270" t="s">
         <v>8</v>
       </c>
-      <c r="H270" s="1">
+      <c r="H270">
         <v>29669</v>
       </c>
       <c r="I270" s="1" t="s">
@@ -10011,7 +10011,7 @@
       <c r="G271" t="s">
         <v>8</v>
       </c>
-      <c r="H271" s="1">
+      <c r="H271">
         <v>29669</v>
       </c>
       <c r="I271" s="1" t="s">
@@ -10040,7 +10040,7 @@
       <c r="G272" t="s">
         <v>8</v>
       </c>
-      <c r="H272" s="1">
+      <c r="H272">
         <v>29669</v>
       </c>
       <c r="I272" s="1" t="s">
@@ -10069,7 +10069,7 @@
       <c r="G273" t="s">
         <v>8</v>
       </c>
-      <c r="H273" s="1">
+      <c r="H273">
         <v>29669</v>
       </c>
       <c r="I273" s="1" t="s">
@@ -10098,7 +10098,7 @@
       <c r="G274" t="s">
         <v>8</v>
       </c>
-      <c r="H274" s="1">
+      <c r="H274">
         <v>29669</v>
       </c>
       <c r="I274" s="1" t="s">
@@ -10127,7 +10127,7 @@
       <c r="G275" t="s">
         <v>8</v>
       </c>
-      <c r="H275" s="1">
+      <c r="H275">
         <v>29669</v>
       </c>
       <c r="I275" s="1" t="s">
@@ -10156,7 +10156,7 @@
       <c r="G276" t="s">
         <v>8</v>
       </c>
-      <c r="H276" s="1">
+      <c r="H276">
         <v>29669</v>
       </c>
       <c r="I276" s="1" t="s">
@@ -10185,7 +10185,7 @@
       <c r="G277" t="s">
         <v>8</v>
       </c>
-      <c r="H277" s="1">
+      <c r="H277">
         <v>29669</v>
       </c>
       <c r="I277" s="1" t="s">
@@ -10214,7 +10214,7 @@
       <c r="G278" t="s">
         <v>8</v>
       </c>
-      <c r="H278" s="1">
+      <c r="H278">
         <v>29669</v>
       </c>
       <c r="I278" s="1" t="s">
@@ -10243,7 +10243,7 @@
       <c r="G279" t="s">
         <v>8</v>
       </c>
-      <c r="H279" s="1">
+      <c r="H279">
         <v>29669</v>
       </c>
       <c r="I279" s="1" t="s">
@@ -10272,7 +10272,7 @@
       <c r="G280" t="s">
         <v>8</v>
       </c>
-      <c r="H280" s="1">
+      <c r="H280">
         <v>29669</v>
       </c>
       <c r="I280" s="1" t="s">
@@ -10301,7 +10301,7 @@
       <c r="G281" t="s">
         <v>8</v>
       </c>
-      <c r="H281" s="1">
+      <c r="H281">
         <v>29669</v>
       </c>
       <c r="I281" s="1" t="s">
@@ -10330,7 +10330,7 @@
       <c r="G282" t="s">
         <v>8</v>
       </c>
-      <c r="H282" s="1">
+      <c r="H282">
         <v>29669</v>
       </c>
       <c r="I282" s="1" t="s">
@@ -10359,7 +10359,7 @@
       <c r="G283" t="s">
         <v>8</v>
       </c>
-      <c r="H283" s="1">
+      <c r="H283">
         <v>29669</v>
       </c>
       <c r="I283" s="1" t="s">
@@ -10388,7 +10388,7 @@
       <c r="G284" t="s">
         <v>8</v>
       </c>
-      <c r="H284" s="1">
+      <c r="H284">
         <v>29669</v>
       </c>
       <c r="I284" s="1" t="s">
@@ -10417,7 +10417,7 @@
       <c r="G285" t="s">
         <v>8</v>
       </c>
-      <c r="H285" s="1">
+      <c r="H285">
         <v>29669</v>
       </c>
       <c r="I285" s="1" t="s">
@@ -10446,7 +10446,7 @@
       <c r="G286" t="s">
         <v>8</v>
       </c>
-      <c r="H286" s="1">
+      <c r="H286">
         <v>29669</v>
       </c>
       <c r="I286" s="1" t="s">
@@ -10475,7 +10475,7 @@
       <c r="G287" t="s">
         <v>8</v>
       </c>
-      <c r="H287" s="1">
+      <c r="H287">
         <v>29669</v>
       </c>
       <c r="I287" s="1" t="s">
@@ -10504,7 +10504,7 @@
       <c r="G288" t="s">
         <v>8</v>
       </c>
-      <c r="H288" s="1">
+      <c r="H288">
         <v>29669</v>
       </c>
       <c r="I288" s="1" t="s">
@@ -10533,7 +10533,7 @@
       <c r="G289" t="s">
         <v>8</v>
       </c>
-      <c r="H289" s="1">
+      <c r="H289">
         <v>29669</v>
       </c>
       <c r="I289" s="1" t="s">
@@ -10562,7 +10562,7 @@
       <c r="G290" t="s">
         <v>8</v>
       </c>
-      <c r="H290" s="1">
+      <c r="H290">
         <v>29669</v>
       </c>
       <c r="I290" s="1" t="s">
@@ -10591,7 +10591,7 @@
       <c r="G291" t="s">
         <v>8</v>
       </c>
-      <c r="H291" s="1">
+      <c r="H291">
         <v>29669</v>
       </c>
       <c r="I291" s="1" t="s">
@@ -10620,7 +10620,7 @@
       <c r="G292" t="s">
         <v>8</v>
       </c>
-      <c r="H292" s="1">
+      <c r="H292">
         <v>29669</v>
       </c>
       <c r="I292" s="1" t="s">
@@ -10649,7 +10649,7 @@
       <c r="G293" t="s">
         <v>8</v>
       </c>
-      <c r="H293" s="1">
+      <c r="H293">
         <v>29669</v>
       </c>
       <c r="I293" s="1" t="s">
@@ -10678,7 +10678,7 @@
       <c r="G294" t="s">
         <v>8</v>
       </c>
-      <c r="H294" s="1">
+      <c r="H294">
         <v>29669</v>
       </c>
       <c r="I294" s="1" t="s">
@@ -10707,7 +10707,7 @@
       <c r="G295" t="s">
         <v>8</v>
       </c>
-      <c r="H295" s="1">
+      <c r="H295">
         <v>29669</v>
       </c>
       <c r="I295" s="1" t="s">
@@ -10736,7 +10736,7 @@
       <c r="G296" t="s">
         <v>8</v>
       </c>
-      <c r="H296" s="1">
+      <c r="H296">
         <v>29669</v>
       </c>
       <c r="I296" s="1" t="s">
@@ -10765,7 +10765,7 @@
       <c r="G297" t="s">
         <v>8</v>
       </c>
-      <c r="H297" s="1">
+      <c r="H297">
         <v>29669</v>
       </c>
       <c r="I297" s="1" t="s">
@@ -10794,7 +10794,7 @@
       <c r="G298" t="s">
         <v>8</v>
       </c>
-      <c r="H298" s="1">
+      <c r="H298">
         <v>29669</v>
       </c>
       <c r="I298" s="1" t="s">
@@ -10823,7 +10823,7 @@
       <c r="G299" t="s">
         <v>8</v>
       </c>
-      <c r="H299" s="1">
+      <c r="H299">
         <v>29669</v>
       </c>
       <c r="I299" s="1" t="s">
@@ -10852,7 +10852,7 @@
       <c r="G300" t="s">
         <v>8</v>
       </c>
-      <c r="H300" s="1">
+      <c r="H300">
         <v>29669</v>
       </c>
       <c r="I300" s="1" t="s">
@@ -10881,7 +10881,7 @@
       <c r="G301" t="s">
         <v>8</v>
       </c>
-      <c r="H301" s="1">
+      <c r="H301">
         <v>29669</v>
       </c>
       <c r="I301" s="1" t="s">
@@ -10910,7 +10910,7 @@
       <c r="G302" t="s">
         <v>8</v>
       </c>
-      <c r="H302" s="1">
+      <c r="H302">
         <v>29669</v>
       </c>
       <c r="I302" s="1" t="s">
@@ -10939,7 +10939,7 @@
       <c r="G303" t="s">
         <v>8</v>
       </c>
-      <c r="H303" s="1">
+      <c r="H303">
         <v>29669</v>
       </c>
       <c r="I303" s="1" t="s">
@@ -10968,7 +10968,7 @@
       <c r="G304" t="s">
         <v>8</v>
       </c>
-      <c r="H304" s="1">
+      <c r="H304">
         <v>29669</v>
       </c>
       <c r="I304" s="1" t="s">
@@ -10997,7 +10997,7 @@
       <c r="G305" t="s">
         <v>8</v>
       </c>
-      <c r="H305" s="1">
+      <c r="H305">
         <v>29669</v>
       </c>
       <c r="I305" s="1" t="s">
@@ -11026,7 +11026,7 @@
       <c r="G306" t="s">
         <v>8</v>
       </c>
-      <c r="H306" s="1">
+      <c r="H306">
         <v>29669</v>
       </c>
       <c r="I306" s="1" t="s">
@@ -11055,7 +11055,7 @@
       <c r="G307" t="s">
         <v>8</v>
       </c>
-      <c r="H307" s="1">
+      <c r="H307">
         <v>29669</v>
       </c>
       <c r="I307" s="1" t="s">
@@ -11084,7 +11084,7 @@
       <c r="G308" t="s">
         <v>8</v>
       </c>
-      <c r="H308" s="1">
+      <c r="H308">
         <v>29669</v>
       </c>
       <c r="I308" s="1" t="s">
@@ -11113,7 +11113,7 @@
       <c r="G309" t="s">
         <v>8</v>
       </c>
-      <c r="H309" s="1">
+      <c r="H309">
         <v>29669</v>
       </c>
       <c r="I309" s="1" t="s">
@@ -11142,7 +11142,7 @@
       <c r="G310" t="s">
         <v>8</v>
       </c>
-      <c r="H310" s="1">
+      <c r="H310">
         <v>29669</v>
       </c>
       <c r="I310" s="1" t="s">
@@ -11171,7 +11171,7 @@
       <c r="G311" t="s">
         <v>8</v>
       </c>
-      <c r="H311" s="1">
+      <c r="H311">
         <v>29669</v>
       </c>
       <c r="I311" s="1" t="s">
@@ -11200,7 +11200,7 @@
       <c r="G312" t="s">
         <v>8</v>
       </c>
-      <c r="H312" s="1">
+      <c r="H312">
         <v>29669</v>
       </c>
       <c r="I312" s="1" t="s">
@@ -11229,7 +11229,7 @@
       <c r="G313" t="s">
         <v>8</v>
       </c>
-      <c r="H313" s="1">
+      <c r="H313">
         <v>29669</v>
       </c>
       <c r="I313" s="1" t="s">
@@ -11258,7 +11258,7 @@
       <c r="G314" t="s">
         <v>8</v>
       </c>
-      <c r="H314" s="1">
+      <c r="H314">
         <v>29669</v>
       </c>
       <c r="I314" s="1" t="s">
@@ -11287,7 +11287,7 @@
       <c r="G315" t="s">
         <v>8</v>
       </c>
-      <c r="H315" s="1">
+      <c r="H315">
         <v>29669</v>
       </c>
       <c r="I315" s="1" t="s">
@@ -11316,7 +11316,7 @@
       <c r="G316" t="s">
         <v>8</v>
       </c>
-      <c r="H316" s="1">
+      <c r="H316">
         <v>29669</v>
       </c>
       <c r="I316" s="1" t="s">
@@ -11345,7 +11345,7 @@
       <c r="G317" t="s">
         <v>8</v>
       </c>
-      <c r="H317" s="1">
+      <c r="H317">
         <v>29669</v>
       </c>
       <c r="I317" s="1" t="s">
@@ -11374,7 +11374,7 @@
       <c r="G318" t="s">
         <v>8</v>
       </c>
-      <c r="H318" s="1">
+      <c r="H318">
         <v>29669</v>
       </c>
       <c r="I318" s="1" t="s">
@@ -11403,7 +11403,7 @@
       <c r="G319" t="s">
         <v>8</v>
       </c>
-      <c r="H319" s="1">
+      <c r="H319">
         <v>29669</v>
       </c>
       <c r="I319" s="1" t="s">
@@ -11432,7 +11432,7 @@
       <c r="G320" t="s">
         <v>8</v>
       </c>
-      <c r="H320" s="1">
+      <c r="H320">
         <v>29669</v>
       </c>
       <c r="I320" s="1" t="s">
@@ -11461,7 +11461,7 @@
       <c r="G321" t="s">
         <v>8</v>
       </c>
-      <c r="H321" s="1">
+      <c r="H321">
         <v>29669</v>
       </c>
       <c r="I321" s="1" t="s">
@@ -11490,7 +11490,7 @@
       <c r="G322" t="s">
         <v>8</v>
       </c>
-      <c r="H322" s="1">
+      <c r="H322">
         <v>29669</v>
       </c>
       <c r="I322" s="1" t="s">
@@ -11519,7 +11519,7 @@
       <c r="G323" t="s">
         <v>8</v>
       </c>
-      <c r="H323" s="1">
+      <c r="H323">
         <v>29669</v>
       </c>
       <c r="I323" s="1" t="s">
@@ -11548,7 +11548,7 @@
       <c r="G324" t="s">
         <v>8</v>
       </c>
-      <c r="H324" s="1">
+      <c r="H324">
         <v>29669</v>
       </c>
       <c r="I324" s="1" t="s">
@@ -11577,7 +11577,7 @@
       <c r="G325" t="s">
         <v>8</v>
       </c>
-      <c r="H325" s="1">
+      <c r="H325">
         <v>29669</v>
       </c>
       <c r="I325" s="1" t="s">
@@ -11606,7 +11606,7 @@
       <c r="G326" t="s">
         <v>8</v>
       </c>
-      <c r="H326" s="1">
+      <c r="H326">
         <v>29669</v>
       </c>
       <c r="I326" s="1" t="s">
@@ -11635,7 +11635,7 @@
       <c r="G327" t="s">
         <v>8</v>
       </c>
-      <c r="H327" s="1">
+      <c r="H327">
         <v>29669</v>
       </c>
       <c r="I327" s="1" t="s">
@@ -11664,7 +11664,7 @@
       <c r="G328" t="s">
         <v>8</v>
       </c>
-      <c r="H328" s="1">
+      <c r="H328">
         <v>29669</v>
       </c>
       <c r="I328" s="1" t="s">
@@ -11693,7 +11693,7 @@
       <c r="G329" t="s">
         <v>8</v>
       </c>
-      <c r="H329" s="1">
+      <c r="H329">
         <v>29669</v>
       </c>
       <c r="I329" s="1" t="s">
@@ -11722,7 +11722,7 @@
       <c r="G330" t="s">
         <v>8</v>
       </c>
-      <c r="H330" s="1">
+      <c r="H330">
         <v>29669</v>
       </c>
       <c r="I330" s="1" t="s">
@@ -11751,7 +11751,7 @@
       <c r="G331" t="s">
         <v>8</v>
       </c>
-      <c r="H331" s="1">
+      <c r="H331">
         <v>29669</v>
       </c>
       <c r="I331" s="1" t="s">
@@ -11780,7 +11780,7 @@
       <c r="G332" t="s">
         <v>8</v>
       </c>
-      <c r="H332" s="1">
+      <c r="H332">
         <v>29669</v>
       </c>
       <c r="I332" s="1" t="s">
@@ -11809,7 +11809,7 @@
       <c r="G333" t="s">
         <v>8</v>
       </c>
-      <c r="H333" s="1">
+      <c r="H333">
         <v>29669</v>
       </c>
       <c r="I333" s="1" t="s">
@@ -11838,7 +11838,7 @@
       <c r="G334" t="s">
         <v>8</v>
       </c>
-      <c r="H334" s="1">
+      <c r="H334">
         <v>29669</v>
       </c>
       <c r="I334" s="1" t="s">
@@ -11867,7 +11867,7 @@
       <c r="G335" t="s">
         <v>8</v>
       </c>
-      <c r="H335" s="1">
+      <c r="H335">
         <v>29669</v>
       </c>
       <c r="I335" s="1" t="s">
@@ -11896,7 +11896,7 @@
       <c r="G336" t="s">
         <v>8</v>
       </c>
-      <c r="H336" s="1">
+      <c r="H336">
         <v>29669</v>
       </c>
       <c r="I336" s="1" t="s">
@@ -11925,7 +11925,7 @@
       <c r="G337" t="s">
         <v>8</v>
       </c>
-      <c r="H337" s="1">
+      <c r="H337">
         <v>29669</v>
       </c>
       <c r="I337" s="1" t="s">
@@ -11954,7 +11954,7 @@
       <c r="G338" t="s">
         <v>8</v>
       </c>
-      <c r="H338" s="1">
+      <c r="H338">
         <v>29669</v>
       </c>
       <c r="I338" s="1" t="s">
@@ -11983,7 +11983,7 @@
       <c r="G339" t="s">
         <v>8</v>
       </c>
-      <c r="H339" s="1">
+      <c r="H339">
         <v>29669</v>
       </c>
       <c r="I339" s="1" t="s">
@@ -12012,7 +12012,7 @@
       <c r="G340" t="s">
         <v>8</v>
       </c>
-      <c r="H340" s="1">
+      <c r="H340">
         <v>29669</v>
       </c>
       <c r="I340" s="1" t="s">
@@ -12041,7 +12041,7 @@
       <c r="G341" t="s">
         <v>8</v>
       </c>
-      <c r="H341" s="1">
+      <c r="H341">
         <v>29669</v>
       </c>
       <c r="I341" s="1" t="s">
@@ -12070,7 +12070,7 @@
       <c r="G342" t="s">
         <v>8</v>
       </c>
-      <c r="H342" s="1">
+      <c r="H342">
         <v>29669</v>
       </c>
       <c r="I342" s="1" t="s">
@@ -12099,7 +12099,7 @@
       <c r="G343" t="s">
         <v>8</v>
       </c>
-      <c r="H343" s="1">
+      <c r="H343">
         <v>29669</v>
       </c>
       <c r="I343" s="1" t="s">
@@ -12128,7 +12128,7 @@
       <c r="G344" t="s">
         <v>8</v>
       </c>
-      <c r="H344" s="1">
+      <c r="H344">
         <v>29669</v>
       </c>
       <c r="I344" s="1" t="s">
@@ -12157,7 +12157,7 @@
       <c r="G345" t="s">
         <v>8</v>
       </c>
-      <c r="H345" s="1">
+      <c r="H345">
         <v>29669</v>
       </c>
       <c r="I345" s="1" t="s">
@@ -12186,7 +12186,7 @@
       <c r="G346" t="s">
         <v>8</v>
       </c>
-      <c r="H346" s="1">
+      <c r="H346">
         <v>29669</v>
       </c>
       <c r="I346" s="1" t="s">
@@ -12215,7 +12215,7 @@
       <c r="G347" t="s">
         <v>8</v>
       </c>
-      <c r="H347" s="1">
+      <c r="H347">
         <v>29669</v>
       </c>
       <c r="I347" s="1" t="s">
@@ -12244,7 +12244,7 @@
       <c r="G348" t="s">
         <v>8</v>
       </c>
-      <c r="H348" s="1">
+      <c r="H348">
         <v>29669</v>
       </c>
       <c r="I348" s="1" t="s">
@@ -12273,7 +12273,7 @@
       <c r="G349" t="s">
         <v>8</v>
       </c>
-      <c r="H349" s="1">
+      <c r="H349">
         <v>29669</v>
       </c>
       <c r="I349" s="1" t="s">
@@ -12302,7 +12302,7 @@
       <c r="G350" t="s">
         <v>8</v>
       </c>
-      <c r="H350" s="1">
+      <c r="H350">
         <v>29669</v>
       </c>
       <c r="I350" s="1" t="s">
@@ -12331,7 +12331,7 @@
       <c r="G351" t="s">
         <v>8</v>
       </c>
-      <c r="H351" s="1">
+      <c r="H351">
         <v>29669</v>
       </c>
       <c r="I351" s="1" t="s">
@@ -12360,7 +12360,7 @@
       <c r="G352" t="s">
         <v>8</v>
       </c>
-      <c r="H352" s="1">
+      <c r="H352">
         <v>29669</v>
       </c>
       <c r="I352" s="1" t="s">
@@ -12389,7 +12389,7 @@
       <c r="G353" t="s">
         <v>8</v>
       </c>
-      <c r="H353" s="1">
+      <c r="H353">
         <v>29669</v>
       </c>
       <c r="I353" s="1" t="s">
@@ -12418,7 +12418,7 @@
       <c r="G354" t="s">
         <v>8</v>
       </c>
-      <c r="H354" s="1">
+      <c r="H354">
         <v>29669</v>
       </c>
       <c r="I354" s="1" t="s">
@@ -12447,7 +12447,7 @@
       <c r="G355" t="s">
         <v>8</v>
       </c>
-      <c r="H355" s="1">
+      <c r="H355">
         <v>29669</v>
       </c>
       <c r="I355" s="1" t="s">
@@ -12476,7 +12476,7 @@
       <c r="G356" t="s">
         <v>8</v>
       </c>
-      <c r="H356" s="1">
+      <c r="H356">
         <v>29669</v>
       </c>
       <c r="I356" s="1" t="s">
@@ -12505,7 +12505,7 @@
       <c r="G357" t="s">
         <v>8</v>
       </c>
-      <c r="H357" s="1">
+      <c r="H357">
         <v>29669</v>
       </c>
       <c r="I357" s="1" t="s">
@@ -12534,7 +12534,7 @@
       <c r="G358" t="s">
         <v>8</v>
       </c>
-      <c r="H358" s="1">
+      <c r="H358">
         <v>29669</v>
       </c>
       <c r="I358" s="1" t="s">
@@ -12563,7 +12563,7 @@
       <c r="G359" t="s">
         <v>8</v>
       </c>
-      <c r="H359" s="1">
+      <c r="H359">
         <v>29669</v>
       </c>
       <c r="I359" s="1" t="s">
@@ -12592,7 +12592,7 @@
       <c r="G360" t="s">
         <v>8</v>
       </c>
-      <c r="H360" s="1">
+      <c r="H360">
         <v>29669</v>
       </c>
       <c r="I360" s="1" t="s">
@@ -12621,7 +12621,7 @@
       <c r="G361" t="s">
         <v>8</v>
       </c>
-      <c r="H361" s="1">
+      <c r="H361">
         <v>29669</v>
       </c>
       <c r="I361" s="1" t="s">
@@ -12650,7 +12650,7 @@
       <c r="G362" t="s">
         <v>8</v>
       </c>
-      <c r="H362" s="1">
+      <c r="H362">
         <v>29669</v>
       </c>
       <c r="I362" s="1" t="s">
@@ -12679,7 +12679,7 @@
       <c r="G363" t="s">
         <v>8</v>
       </c>
-      <c r="H363" s="1">
+      <c r="H363">
         <v>29669</v>
       </c>
       <c r="I363" s="1" t="s">
@@ -12708,7 +12708,7 @@
       <c r="G364" t="s">
         <v>8</v>
       </c>
-      <c r="H364" s="1">
+      <c r="H364">
         <v>29669</v>
       </c>
       <c r="I364" s="1" t="s">
@@ -12737,7 +12737,7 @@
       <c r="G365" t="s">
         <v>8</v>
       </c>
-      <c r="H365" s="1">
+      <c r="H365">
         <v>29669</v>
       </c>
       <c r="I365" s="1" t="s">
@@ -12766,7 +12766,7 @@
       <c r="G366" t="s">
         <v>8</v>
       </c>
-      <c r="H366" s="1">
+      <c r="H366">
         <v>29669</v>
       </c>
       <c r="I366" s="1" t="s">
@@ -12795,7 +12795,7 @@
       <c r="G367" t="s">
         <v>8</v>
       </c>
-      <c r="H367" s="1">
+      <c r="H367">
         <v>29669</v>
       </c>
       <c r="I367" s="1" t="s">
@@ -12824,7 +12824,7 @@
       <c r="G368" t="s">
         <v>8</v>
       </c>
-      <c r="H368" s="1">
+      <c r="H368">
         <v>29669</v>
       </c>
       <c r="I368" s="1" t="s">
@@ -12853,7 +12853,7 @@
       <c r="G369" t="s">
         <v>8</v>
       </c>
-      <c r="H369" s="1">
+      <c r="H369">
         <v>29669</v>
       </c>
       <c r="I369" s="1" t="s">
@@ -12882,7 +12882,7 @@
       <c r="G370" t="s">
         <v>8</v>
       </c>
-      <c r="H370" s="1">
+      <c r="H370">
         <v>29669</v>
       </c>
       <c r="I370" s="1" t="s">
@@ -12911,7 +12911,7 @@
       <c r="G371" t="s">
         <v>8</v>
       </c>
-      <c r="H371" s="1">
+      <c r="H371">
         <v>29669</v>
       </c>
       <c r="I371" s="1" t="s">
@@ -12940,7 +12940,7 @@
       <c r="G372" t="s">
         <v>8</v>
       </c>
-      <c r="H372" s="1">
+      <c r="H372">
         <v>29669</v>
       </c>
       <c r="I372" s="1" t="s">
@@ -12969,7 +12969,7 @@
       <c r="G373" t="s">
         <v>8</v>
       </c>
-      <c r="H373" s="1">
+      <c r="H373">
         <v>29669</v>
       </c>
       <c r="I373" s="1" t="s">
@@ -12998,7 +12998,7 @@
       <c r="G374" t="s">
         <v>8</v>
       </c>
-      <c r="H374" s="1">
+      <c r="H374">
         <v>29669</v>
       </c>
       <c r="I374" s="1" t="s">
@@ -13027,7 +13027,7 @@
       <c r="G375" t="s">
         <v>8</v>
       </c>
-      <c r="H375" s="1">
+      <c r="H375">
         <v>29669</v>
       </c>
       <c r="I375" s="1" t="s">
@@ -13056,7 +13056,7 @@
       <c r="G376" t="s">
         <v>8</v>
       </c>
-      <c r="H376" s="1">
+      <c r="H376">
         <v>29669</v>
       </c>
       <c r="I376" s="1" t="s">
@@ -13085,7 +13085,7 @@
       <c r="G377" t="s">
         <v>8</v>
       </c>
-      <c r="H377" s="1">
+      <c r="H377">
         <v>29669</v>
       </c>
       <c r="I377" s="1" t="s">
@@ -13114,7 +13114,7 @@
       <c r="G378" t="s">
         <v>8</v>
       </c>
-      <c r="H378" s="1">
+      <c r="H378">
         <v>29669</v>
       </c>
       <c r="I378" s="1" t="s">
@@ -13143,7 +13143,7 @@
       <c r="G379" t="s">
         <v>8</v>
       </c>
-      <c r="H379" s="1">
+      <c r="H379">
         <v>29669</v>
       </c>
       <c r="I379" s="1" t="s">
@@ -13172,7 +13172,7 @@
       <c r="G380" t="s">
         <v>8</v>
       </c>
-      <c r="H380" s="1">
+      <c r="H380">
         <v>29669</v>
       </c>
       <c r="I380" s="1" t="s">
@@ -13201,7 +13201,7 @@
       <c r="G381" t="s">
         <v>8</v>
       </c>
-      <c r="H381" s="1">
+      <c r="H381">
         <v>29669</v>
       </c>
       <c r="I381" s="1" t="s">
@@ -13230,7 +13230,7 @@
       <c r="G382" t="s">
         <v>8</v>
       </c>
-      <c r="H382" s="1">
+      <c r="H382">
         <v>29669</v>
       </c>
       <c r="I382" s="1" t="s">
@@ -13259,7 +13259,7 @@
       <c r="G383" t="s">
         <v>8</v>
       </c>
-      <c r="H383" s="1">
+      <c r="H383">
         <v>29669</v>
       </c>
       <c r="I383" s="1" t="s">
@@ -13288,7 +13288,7 @@
       <c r="G384" t="s">
         <v>8</v>
       </c>
-      <c r="H384" s="1">
+      <c r="H384">
         <v>29669</v>
       </c>
       <c r="I384" s="1" t="s">
@@ -13317,7 +13317,7 @@
       <c r="G385" t="s">
         <v>8</v>
       </c>
-      <c r="H385" s="1">
+      <c r="H385">
         <v>29669</v>
       </c>
       <c r="I385" s="1" t="s">
@@ -13346,7 +13346,7 @@
       <c r="G386" t="s">
         <v>8</v>
       </c>
-      <c r="H386" s="1">
+      <c r="H386">
         <v>29669</v>
       </c>
       <c r="I386" s="1" t="s">
@@ -13375,7 +13375,7 @@
       <c r="G387" t="s">
         <v>8</v>
       </c>
-      <c r="H387" s="1">
+      <c r="H387">
         <v>29669</v>
       </c>
       <c r="I387" s="1" t="s">
@@ -13404,7 +13404,7 @@
       <c r="G388" t="s">
         <v>8</v>
       </c>
-      <c r="H388" s="1">
+      <c r="H388">
         <v>29669</v>
       </c>
       <c r="I388" s="1" t="s">
@@ -13433,7 +13433,7 @@
       <c r="G389" t="s">
         <v>8</v>
       </c>
-      <c r="H389" s="1">
+      <c r="H389">
         <v>29669</v>
       </c>
       <c r="I389" s="1" t="s">
@@ -13462,7 +13462,7 @@
       <c r="G390" t="s">
         <v>8</v>
       </c>
-      <c r="H390" s="1">
+      <c r="H390">
         <v>29669</v>
       </c>
       <c r="I390" s="1" t="s">
@@ -13491,7 +13491,7 @@
       <c r="G391" t="s">
         <v>8</v>
       </c>
-      <c r="H391" s="1">
+      <c r="H391">
         <v>29669</v>
       </c>
       <c r="I391" s="1" t="s">
@@ -13520,7 +13520,7 @@
       <c r="G392" t="s">
         <v>8</v>
       </c>
-      <c r="H392" s="1">
+      <c r="H392">
         <v>29669</v>
       </c>
       <c r="I392" s="1" t="s">
@@ -13549,7 +13549,7 @@
       <c r="G393" t="s">
         <v>8</v>
       </c>
-      <c r="H393" s="1">
+      <c r="H393">
         <v>29669</v>
       </c>
       <c r="I393" s="1" t="s">
@@ -13578,7 +13578,7 @@
       <c r="G394" t="s">
         <v>8</v>
       </c>
-      <c r="H394" s="1">
+      <c r="H394">
         <v>29669</v>
       </c>
       <c r="I394" s="1" t="s">
@@ -13607,7 +13607,7 @@
       <c r="G395" t="s">
         <v>8</v>
       </c>
-      <c r="H395" s="1">
+      <c r="H395">
         <v>29669</v>
       </c>
       <c r="I395" s="1" t="s">
@@ -13636,7 +13636,7 @@
       <c r="G396" t="s">
         <v>8</v>
       </c>
-      <c r="H396" s="1">
+      <c r="H396">
         <v>29669</v>
       </c>
       <c r="I396" s="1" t="s">
@@ -13665,7 +13665,7 @@
       <c r="G397" t="s">
         <v>8</v>
       </c>
-      <c r="H397" s="1">
+      <c r="H397">
         <v>29669</v>
       </c>
       <c r="I397" s="1" t="s">
@@ -13694,7 +13694,7 @@
       <c r="G398" t="s">
         <v>8</v>
       </c>
-      <c r="H398" s="1">
+      <c r="H398">
         <v>29669</v>
       </c>
       <c r="I398" s="1" t="s">
@@ -13723,7 +13723,7 @@
       <c r="G399" t="s">
         <v>8</v>
       </c>
-      <c r="H399" s="1">
+      <c r="H399">
         <v>29669</v>
       </c>
       <c r="I399" s="1" t="s">
@@ -13752,7 +13752,7 @@
       <c r="G400" t="s">
         <v>8</v>
       </c>
-      <c r="H400" s="1">
+      <c r="H400">
         <v>29669</v>
       </c>
       <c r="I400" s="1" t="s">
@@ -13781,7 +13781,7 @@
       <c r="G401" t="s">
         <v>8</v>
       </c>
-      <c r="H401" s="1">
+      <c r="H401">
         <v>29669</v>
       </c>
       <c r="I401" s="1" t="s">
@@ -13810,7 +13810,7 @@
       <c r="G402" t="s">
         <v>8</v>
       </c>
-      <c r="H402" s="1">
+      <c r="H402">
         <v>29669</v>
       </c>
       <c r="I402" s="1" t="s">
@@ -13839,7 +13839,7 @@
       <c r="G403" t="s">
         <v>8</v>
       </c>
-      <c r="H403" s="1">
+      <c r="H403">
         <v>29669</v>
       </c>
       <c r="I403" s="1" t="s">
@@ -13868,7 +13868,7 @@
       <c r="G404" t="s">
         <v>8</v>
       </c>
-      <c r="H404" s="1">
+      <c r="H404">
         <v>29669</v>
       </c>
       <c r="I404" s="1" t="s">
@@ -13897,7 +13897,7 @@
       <c r="G405" t="s">
         <v>8</v>
       </c>
-      <c r="H405" s="1">
+      <c r="H405">
         <v>29669</v>
       </c>
       <c r="I405" s="1" t="s">
@@ -13926,7 +13926,7 @@
       <c r="G406" t="s">
         <v>8</v>
       </c>
-      <c r="H406" s="1">
+      <c r="H406">
         <v>29669</v>
       </c>
       <c r="I406" s="1" t="s">
@@ -13955,7 +13955,7 @@
       <c r="G407" t="s">
         <v>8</v>
       </c>
-      <c r="H407" s="1">
+      <c r="H407">
         <v>29669</v>
       </c>
       <c r="I407" s="1" t="s">
@@ -13984,7 +13984,7 @@
       <c r="G408" t="s">
         <v>8</v>
       </c>
-      <c r="H408" s="1">
+      <c r="H408">
         <v>29669</v>
       </c>
       <c r="I408" s="1" t="s">
@@ -14013,7 +14013,7 @@
       <c r="G409" t="s">
         <v>8</v>
       </c>
-      <c r="H409" s="1">
+      <c r="H409">
         <v>29669</v>
       </c>
       <c r="I409" s="1" t="s">
@@ -14042,7 +14042,7 @@
       <c r="G410" t="s">
         <v>8</v>
       </c>
-      <c r="H410" s="1">
+      <c r="H410">
         <v>29669</v>
       </c>
       <c r="I410" s="1" t="s">
@@ -14071,7 +14071,7 @@
       <c r="G411" t="s">
         <v>8</v>
       </c>
-      <c r="H411" s="1">
+      <c r="H411">
         <v>29669</v>
       </c>
       <c r="I411" s="1" t="s">
@@ -14100,7 +14100,7 @@
       <c r="G412" t="s">
         <v>8</v>
       </c>
-      <c r="H412" s="1">
+      <c r="H412">
         <v>29669</v>
       </c>
       <c r="I412" s="1" t="s">
@@ -14129,7 +14129,7 @@
       <c r="G413" t="s">
         <v>8</v>
       </c>
-      <c r="H413" s="1">
+      <c r="H413">
         <v>29669</v>
       </c>
       <c r="I413" s="1" t="s">
@@ -14158,7 +14158,7 @@
       <c r="G414" t="s">
         <v>8</v>
       </c>
-      <c r="H414" s="1">
+      <c r="H414">
         <v>29669</v>
       </c>
       <c r="I414" s="1" t="s">
@@ -14187,7 +14187,7 @@
       <c r="G415" t="s">
         <v>8</v>
       </c>
-      <c r="H415" s="1">
+      <c r="H415">
         <v>29669</v>
       </c>
       <c r="I415" s="1" t="s">
@@ -14216,7 +14216,7 @@
       <c r="G416" t="s">
         <v>8</v>
       </c>
-      <c r="H416" s="1">
+      <c r="H416">
         <v>29669</v>
       </c>
       <c r="I416" s="1" t="s">
@@ -14245,7 +14245,7 @@
       <c r="G417" t="s">
         <v>8</v>
       </c>
-      <c r="H417" s="1">
+      <c r="H417">
         <v>29669</v>
       </c>
       <c r="I417" s="1" t="s">
@@ -14274,7 +14274,7 @@
       <c r="G418" t="s">
         <v>8</v>
       </c>
-      <c r="H418" s="1">
+      <c r="H418">
         <v>29669</v>
       </c>
       <c r="I418" s="1" t="s">
@@ -14303,7 +14303,7 @@
       <c r="G419" t="s">
         <v>8</v>
       </c>
-      <c r="H419" s="1">
+      <c r="H419">
         <v>29669</v>
       </c>
       <c r="I419" s="1" t="s">
@@ -14332,7 +14332,7 @@
       <c r="G420" t="s">
         <v>8</v>
       </c>
-      <c r="H420" s="1">
+      <c r="H420">
         <v>29669</v>
       </c>
       <c r="I420" s="1" t="s">
@@ -14361,7 +14361,7 @@
       <c r="G421" t="s">
         <v>8</v>
       </c>
-      <c r="H421" s="1">
+      <c r="H421">
         <v>29669</v>
       </c>
       <c r="I421" s="1" t="s">
@@ -14390,7 +14390,7 @@
       <c r="G422" t="s">
         <v>8</v>
       </c>
-      <c r="H422" s="1">
+      <c r="H422">
         <v>29669</v>
       </c>
       <c r="I422" s="1" t="s">
@@ -14419,7 +14419,7 @@
       <c r="G423" t="s">
         <v>8</v>
       </c>
-      <c r="H423" s="1">
+      <c r="H423">
         <v>29669</v>
       </c>
       <c r="I423" s="1" t="s">
@@ -14448,7 +14448,7 @@
       <c r="G424" t="s">
         <v>8</v>
       </c>
-      <c r="H424" s="1">
+      <c r="H424">
         <v>29669</v>
       </c>
       <c r="I424" s="1" t="s">
@@ -14477,7 +14477,7 @@
       <c r="G425" t="s">
         <v>8</v>
       </c>
-      <c r="H425" s="1">
+      <c r="H425">
         <v>29669</v>
       </c>
       <c r="I425" s="1" t="s">
@@ -14506,7 +14506,7 @@
       <c r="G426" t="s">
         <v>8</v>
       </c>
-      <c r="H426" s="1">
+      <c r="H426">
         <v>29669</v>
       </c>
       <c r="I426" s="1" t="s">
@@ -14535,7 +14535,7 @@
       <c r="G427" t="s">
         <v>8</v>
       </c>
-      <c r="H427" s="1">
+      <c r="H427">
         <v>29669</v>
       </c>
       <c r="I427" s="1" t="s">
@@ -14564,7 +14564,7 @@
       <c r="G428" t="s">
         <v>8</v>
       </c>
-      <c r="H428" s="1">
+      <c r="H428">
         <v>29669</v>
       </c>
       <c r="I428" s="1" t="s">
@@ -14593,7 +14593,7 @@
       <c r="G429" t="s">
         <v>8</v>
       </c>
-      <c r="H429" s="1">
+      <c r="H429">
         <v>29669</v>
       </c>
       <c r="I429" s="1" t="s">
@@ -14622,7 +14622,7 @@
       <c r="G430" t="s">
         <v>8</v>
       </c>
-      <c r="H430" s="1">
+      <c r="H430">
         <v>29669</v>
       </c>
       <c r="I430" s="1" t="s">
@@ -14651,7 +14651,7 @@
       <c r="G431" t="s">
         <v>8</v>
       </c>
-      <c r="H431" s="1">
+      <c r="H431">
         <v>29669</v>
       </c>
       <c r="I431" s="1" t="s">
@@ -14680,7 +14680,7 @@
       <c r="G432" t="s">
         <v>8</v>
       </c>
-      <c r="H432" s="1">
+      <c r="H432">
         <v>29669</v>
       </c>
       <c r="I432" s="1" t="s">
@@ -14709,7 +14709,7 @@
       <c r="G433" t="s">
         <v>8</v>
       </c>
-      <c r="H433" s="1">
+      <c r="H433">
         <v>29669</v>
       </c>
       <c r="I433" s="1" t="s">
@@ -14738,7 +14738,7 @@
       <c r="G434" t="s">
         <v>8</v>
       </c>
-      <c r="H434" s="1">
+      <c r="H434">
         <v>29669</v>
       </c>
       <c r="I434" s="1" t="s">
@@ -14767,7 +14767,7 @@
       <c r="G435" t="s">
         <v>8</v>
       </c>
-      <c r="H435" s="1">
+      <c r="H435">
         <v>29669</v>
       </c>
       <c r="I435" s="1" t="s">
@@ -14796,7 +14796,7 @@
       <c r="G436" t="s">
         <v>8</v>
       </c>
-      <c r="H436" s="1">
+      <c r="H436">
         <v>29669</v>
       </c>
       <c r="I436" s="1" t="s">
@@ -14825,7 +14825,7 @@
       <c r="G437" t="s">
         <v>8</v>
       </c>
-      <c r="H437" s="1">
+      <c r="H437">
         <v>29669</v>
       </c>
       <c r="I437" s="1" t="s">
@@ -14854,7 +14854,7 @@
       <c r="G438" t="s">
         <v>8</v>
       </c>
-      <c r="H438" s="1">
+      <c r="H438">
         <v>29669</v>
       </c>
       <c r="I438" s="1" t="s">
@@ -14883,7 +14883,7 @@
       <c r="G439" t="s">
         <v>8</v>
       </c>
-      <c r="H439" s="1">
+      <c r="H439">
         <v>29669</v>
       </c>
       <c r="I439" s="1" t="s">
@@ -14912,7 +14912,7 @@
       <c r="G440" t="s">
         <v>8</v>
       </c>
-      <c r="H440" s="1">
+      <c r="H440">
         <v>29669</v>
       </c>
       <c r="I440" s="1" t="s">
@@ -14941,7 +14941,7 @@
       <c r="G441" t="s">
         <v>8</v>
       </c>
-      <c r="H441" s="1">
+      <c r="H441">
         <v>29669</v>
       </c>
       <c r="I441" s="1" t="s">
@@ -14970,7 +14970,7 @@
       <c r="G442" t="s">
         <v>8</v>
       </c>
-      <c r="H442" s="1">
+      <c r="H442">
         <v>29669</v>
       </c>
       <c r="I442" s="1" t="s">
@@ -14999,7 +14999,7 @@
       <c r="G443" t="s">
         <v>8</v>
       </c>
-      <c r="H443" s="1">
+      <c r="H443">
         <v>29669</v>
       </c>
       <c r="I443" s="1" t="s">
@@ -15028,7 +15028,7 @@
       <c r="G444" t="s">
         <v>8</v>
       </c>
-      <c r="H444" s="1">
+      <c r="H444">
         <v>29669</v>
       </c>
       <c r="I444" s="1" t="s">
@@ -15057,7 +15057,7 @@
       <c r="G445" t="s">
         <v>8</v>
       </c>
-      <c r="H445" s="1">
+      <c r="H445">
         <v>29669</v>
       </c>
       <c r="I445" s="1" t="s">
@@ -15086,7 +15086,7 @@
       <c r="G446" t="s">
         <v>8</v>
       </c>
-      <c r="H446" s="1">
+      <c r="H446">
         <v>29669</v>
       </c>
       <c r="I446" s="1" t="s">
@@ -15115,7 +15115,7 @@
       <c r="G447" t="s">
         <v>8</v>
       </c>
-      <c r="H447" s="1">
+      <c r="H447">
         <v>29669</v>
       </c>
       <c r="I447" s="1" t="s">
@@ -15144,7 +15144,7 @@
       <c r="G448" t="s">
         <v>8</v>
       </c>
-      <c r="H448" s="1">
+      <c r="H448">
         <v>29669</v>
       </c>
       <c r="I448" s="1" t="s">
@@ -15173,7 +15173,7 @@
       <c r="G449" t="s">
         <v>8</v>
       </c>
-      <c r="H449" s="1">
+      <c r="H449">
         <v>29669</v>
       </c>
       <c r="I449" s="1" t="s">
@@ -15202,7 +15202,7 @@
       <c r="G450" t="s">
         <v>8</v>
       </c>
-      <c r="H450" s="1">
+      <c r="H450">
         <v>29669</v>
       </c>
       <c r="I450" s="1" t="s">
@@ -15231,7 +15231,7 @@
       <c r="G451" t="s">
         <v>8</v>
       </c>
-      <c r="H451" s="1">
+      <c r="H451">
         <v>29669</v>
       </c>
       <c r="I451" s="1" t="s">
@@ -15260,7 +15260,7 @@
       <c r="G452" t="s">
         <v>8</v>
       </c>
-      <c r="H452" s="1">
+      <c r="H452">
         <v>29669</v>
       </c>
       <c r="I452" s="1" t="s">
@@ -15289,7 +15289,7 @@
       <c r="G453" t="s">
         <v>8</v>
       </c>
-      <c r="H453" s="1">
+      <c r="H453">
         <v>29669</v>
       </c>
       <c r="I453" s="1" t="s">
@@ -15318,7 +15318,7 @@
       <c r="G454" t="s">
         <v>8</v>
       </c>
-      <c r="H454" s="1">
+      <c r="H454">
         <v>29669</v>
       </c>
       <c r="I454" s="1" t="s">
@@ -15347,7 +15347,7 @@
       <c r="G455" t="s">
         <v>8</v>
       </c>
-      <c r="H455" s="1">
+      <c r="H455">
         <v>29669</v>
       </c>
       <c r="I455" s="1" t="s">
@@ -15376,7 +15376,7 @@
       <c r="G456" t="s">
         <v>8</v>
       </c>
-      <c r="H456" s="1">
+      <c r="H456">
         <v>29669</v>
       </c>
       <c r="I456" s="1" t="s">
@@ -15405,7 +15405,7 @@
       <c r="G457" t="s">
         <v>8</v>
       </c>
-      <c r="H457" s="1">
+      <c r="H457">
         <v>29669</v>
       </c>
       <c r="I457" s="1" t="s">
@@ -15434,7 +15434,7 @@
       <c r="G458" t="s">
         <v>8</v>
       </c>
-      <c r="H458" s="1">
+      <c r="H458">
         <v>29669</v>
       </c>
       <c r="I458" s="1" t="s">
@@ -15463,7 +15463,7 @@
       <c r="G459" t="s">
         <v>8</v>
       </c>
-      <c r="H459" s="1">
+      <c r="H459">
         <v>29669</v>
       </c>
       <c r="I459" s="1" t="s">
@@ -15492,7 +15492,7 @@
       <c r="G460" t="s">
         <v>8</v>
       </c>
-      <c r="H460" s="1">
+      <c r="H460">
         <v>29669</v>
       </c>
       <c r="I460" s="1" t="s">
@@ -15521,7 +15521,7 @@
       <c r="G461" t="s">
         <v>8</v>
       </c>
-      <c r="H461" s="1">
+      <c r="H461">
         <v>29669</v>
       </c>
       <c r="I461" s="1" t="s">
@@ -15550,7 +15550,7 @@
       <c r="G462" t="s">
         <v>8</v>
       </c>
-      <c r="H462" s="1">
+      <c r="H462">
         <v>29669</v>
       </c>
       <c r="I462" s="1" t="s">
@@ -15579,7 +15579,7 @@
       <c r="G463" t="s">
         <v>8</v>
       </c>
-      <c r="H463" s="1">
+      <c r="H463">
         <v>29669</v>
       </c>
       <c r="I463" s="1" t="s">
@@ -15608,7 +15608,7 @@
       <c r="G464" t="s">
         <v>8</v>
       </c>
-      <c r="H464" s="1">
+      <c r="H464">
         <v>29669</v>
       </c>
       <c r="I464" s="1" t="s">
@@ -15637,7 +15637,7 @@
       <c r="G465" t="s">
         <v>8</v>
       </c>
-      <c r="H465" s="1">
+      <c r="H465">
         <v>29669</v>
       </c>
       <c r="I465" s="1" t="s">
@@ -15666,7 +15666,7 @@
       <c r="G466" t="s">
         <v>8</v>
       </c>
-      <c r="H466" s="1">
+      <c r="H466">
         <v>29669</v>
       </c>
       <c r="I466" s="1" t="s">
@@ -15695,7 +15695,7 @@
       <c r="G467" t="s">
         <v>8</v>
       </c>
-      <c r="H467" s="1">
+      <c r="H467">
         <v>29669</v>
       </c>
       <c r="I467" s="1" t="s">
@@ -15724,7 +15724,7 @@
       <c r="G468" t="s">
         <v>8</v>
       </c>
-      <c r="H468" s="1">
+      <c r="H468">
         <v>29669</v>
       </c>
       <c r="I468" s="1" t="s">
@@ -15753,7 +15753,7 @@
       <c r="G469" t="s">
         <v>8</v>
       </c>
-      <c r="H469" s="1">
+      <c r="H469">
         <v>29669</v>
       </c>
       <c r="I469" s="1" t="s">
@@ -15782,7 +15782,7 @@
       <c r="G470" t="s">
         <v>8</v>
       </c>
-      <c r="H470" s="1">
+      <c r="H470">
         <v>29669</v>
       </c>
       <c r="I470" s="1" t="s">
@@ -15811,7 +15811,7 @@
       <c r="G471" t="s">
         <v>8</v>
       </c>
-      <c r="H471" s="1">
+      <c r="H471">
         <v>29669</v>
       </c>
       <c r="I471" s="1" t="s">
@@ -15840,7 +15840,7 @@
       <c r="G472" t="s">
         <v>8</v>
       </c>
-      <c r="H472" s="1">
+      <c r="H472">
         <v>29669</v>
       </c>
       <c r="I472" s="1" t="s">
@@ -15869,7 +15869,7 @@
       <c r="G473" t="s">
         <v>8</v>
       </c>
-      <c r="H473" s="1">
+      <c r="H473">
         <v>29669</v>
       </c>
       <c r="I473" s="1" t="s">
@@ -15898,7 +15898,7 @@
       <c r="G474" t="s">
         <v>8</v>
       </c>
-      <c r="H474" s="1">
+      <c r="H474">
         <v>29669</v>
       </c>
       <c r="I474" s="1" t="s">
@@ -15927,7 +15927,7 @@
       <c r="G475" t="s">
         <v>8</v>
       </c>
-      <c r="H475" s="1">
+      <c r="H475">
         <v>29669</v>
       </c>
       <c r="I475" s="1" t="s">
@@ -15956,7 +15956,7 @@
       <c r="G476" t="s">
         <v>8</v>
       </c>
-      <c r="H476" s="1">
+      <c r="H476">
         <v>29669</v>
       </c>
       <c r="I476" s="1" t="s">
@@ -15985,7 +15985,7 @@
       <c r="G477" t="s">
         <v>8</v>
       </c>
-      <c r="H477" s="1">
+      <c r="H477">
         <v>29669</v>
       </c>
       <c r="I477" s="1" t="s">
@@ -16014,7 +16014,7 @@
       <c r="G478" t="s">
         <v>8</v>
       </c>
-      <c r="H478" s="1">
+      <c r="H478">
         <v>29669</v>
       </c>
       <c r="I478" s="1" t="s">
@@ -16043,7 +16043,7 @@
       <c r="G479" t="s">
         <v>8</v>
       </c>
-      <c r="H479" s="1">
+      <c r="H479">
         <v>29669</v>
       </c>
       <c r="I479" s="1" t="s">
@@ -16072,7 +16072,7 @@
       <c r="G480" t="s">
         <v>8</v>
       </c>
-      <c r="H480" s="1">
+      <c r="H480">
         <v>29669</v>
       </c>
       <c r="I480" s="1" t="s">
@@ -16101,7 +16101,7 @@
       <c r="G481" t="s">
         <v>8</v>
       </c>
-      <c r="H481" s="1">
+      <c r="H481">
         <v>29669</v>
       </c>
       <c r="I481" s="1" t="s">
@@ -16130,7 +16130,7 @@
       <c r="G482" t="s">
         <v>8</v>
       </c>
-      <c r="H482" s="1">
+      <c r="H482">
         <v>29669</v>
       </c>
       <c r="I482" s="1" t="s">
@@ -16159,7 +16159,7 @@
       <c r="G483" t="s">
         <v>8</v>
       </c>
-      <c r="H483" s="1">
+      <c r="H483">
         <v>29669</v>
       </c>
       <c r="I483" s="1" t="s">
@@ -16188,7 +16188,7 @@
       <c r="G484" t="s">
         <v>8</v>
       </c>
-      <c r="H484" s="1">
+      <c r="H484">
         <v>29669</v>
       </c>
       <c r="I484" s="1" t="s">
@@ -16217,7 +16217,7 @@
       <c r="G485" t="s">
         <v>8</v>
       </c>
-      <c r="H485" s="1">
+      <c r="H485">
         <v>29669</v>
       </c>
       <c r="I485" s="1" t="s">
@@ -16246,7 +16246,7 @@
       <c r="G486" t="s">
         <v>8</v>
       </c>
-      <c r="H486" s="1">
+      <c r="H486">
         <v>29669</v>
       </c>
       <c r="I486" s="1" t="s">
@@ -16275,7 +16275,7 @@
       <c r="G487" t="s">
         <v>8</v>
       </c>
-      <c r="H487" s="1">
+      <c r="H487">
         <v>29669</v>
       </c>
       <c r="I487" s="1" t="s">
@@ -16304,7 +16304,7 @@
       <c r="G488" t="s">
         <v>8</v>
       </c>
-      <c r="H488" s="1">
+      <c r="H488">
         <v>29669</v>
       </c>
       <c r="I488" s="1" t="s">
@@ -16333,7 +16333,7 @@
       <c r="G489" t="s">
         <v>8</v>
       </c>
-      <c r="H489" s="1">
+      <c r="H489">
         <v>29669</v>
       </c>
       <c r="I489" s="1" t="s">
@@ -16362,7 +16362,7 @@
       <c r="G490" t="s">
         <v>8</v>
       </c>
-      <c r="H490" s="1">
+      <c r="H490">
         <v>29669</v>
       </c>
       <c r="I490" s="1" t="s">
@@ -16391,7 +16391,7 @@
       <c r="G491" t="s">
         <v>8</v>
       </c>
-      <c r="H491" s="1">
+      <c r="H491">
         <v>29669</v>
       </c>
       <c r="I491" s="1" t="s">
@@ -16420,7 +16420,7 @@
       <c r="G492" t="s">
         <v>8</v>
       </c>
-      <c r="H492" s="1">
+      <c r="H492">
         <v>29669</v>
       </c>
       <c r="I492" s="1" t="s">
@@ -16449,7 +16449,7 @@
       <c r="G493" t="s">
         <v>8</v>
       </c>
-      <c r="H493" s="1">
+      <c r="H493">
         <v>29669</v>
       </c>
       <c r="I493" s="1" t="s">
@@ -16478,7 +16478,7 @@
       <c r="G494" t="s">
         <v>8</v>
       </c>
-      <c r="H494" s="1">
+      <c r="H494">
         <v>29669</v>
       </c>
       <c r="I494" s="1" t="s">
@@ -16507,7 +16507,7 @@
       <c r="G495" t="s">
         <v>8</v>
       </c>
-      <c r="H495" s="1">
+      <c r="H495">
         <v>29669</v>
       </c>
       <c r="I495" s="1" t="s">
@@ -16536,7 +16536,7 @@
       <c r="G496" t="s">
         <v>8</v>
       </c>
-      <c r="H496" s="1">
+      <c r="H496">
         <v>29669</v>
       </c>
       <c r="I496" s="1" t="s">
@@ -16565,7 +16565,7 @@
       <c r="G497" t="s">
         <v>8</v>
       </c>
-      <c r="H497" s="1">
+      <c r="H497">
         <v>29669</v>
       </c>
       <c r="I497" s="1" t="s">
@@ -16594,7 +16594,7 @@
       <c r="G498" t="s">
         <v>8</v>
       </c>
-      <c r="H498" s="1">
+      <c r="H498">
         <v>29669</v>
       </c>
       <c r="I498" s="1" t="s">
@@ -16623,7 +16623,7 @@
       <c r="G499" t="s">
         <v>8</v>
       </c>
-      <c r="H499" s="1">
+      <c r="H499">
         <v>29669</v>
       </c>
       <c r="I499" s="1" t="s">
@@ -16652,7 +16652,7 @@
       <c r="G500" t="s">
         <v>8</v>
       </c>
-      <c r="H500" s="1">
+      <c r="H500">
         <v>29669</v>
       </c>
       <c r="I500" s="1" t="s">
@@ -16681,7 +16681,7 @@
       <c r="G501" t="s">
         <v>8</v>
       </c>
-      <c r="H501" s="1">
+      <c r="H501">
         <v>29669</v>
       </c>
       <c r="I501" s="1" t="s">
@@ -16710,7 +16710,7 @@
       <c r="G502" t="s">
         <v>8</v>
       </c>
-      <c r="H502" s="1">
+      <c r="H502">
         <v>29669</v>
       </c>
       <c r="I502" s="1" t="s">
@@ -16739,7 +16739,7 @@
       <c r="G503" t="s">
         <v>8</v>
       </c>
-      <c r="H503" s="1">
+      <c r="H503">
         <v>29669</v>
       </c>
       <c r="I503" s="1" t="s">
@@ -16768,7 +16768,7 @@
       <c r="G504" t="s">
         <v>8</v>
       </c>
-      <c r="H504" s="1">
+      <c r="H504">
         <v>29669</v>
       </c>
       <c r="I504" s="1" t="s">
@@ -16797,7 +16797,7 @@
       <c r="G505" t="s">
         <v>8</v>
       </c>
-      <c r="H505" s="1">
+      <c r="H505">
         <v>29669</v>
       </c>
       <c r="I505" s="1" t="s">
@@ -16826,7 +16826,7 @@
       <c r="G506" t="s">
         <v>8</v>
       </c>
-      <c r="H506" s="1">
+      <c r="H506">
         <v>29669</v>
       </c>
       <c r="I506" s="1" t="s">
@@ -16855,7 +16855,7 @@
       <c r="G507" t="s">
         <v>8</v>
       </c>
-      <c r="H507" s="1">
+      <c r="H507">
         <v>29669</v>
       </c>
       <c r="I507" s="1" t="s">
@@ -16884,7 +16884,7 @@
       <c r="G508" t="s">
         <v>8</v>
       </c>
-      <c r="H508" s="1">
+      <c r="H508">
         <v>29669</v>
       </c>
       <c r="I508" s="1" t="s">
@@ -16913,7 +16913,7 @@
       <c r="G509" t="s">
         <v>8</v>
       </c>
-      <c r="H509" s="1">
+      <c r="H509">
         <v>29669</v>
       </c>
       <c r="I509" s="1" t="s">
@@ -16942,7 +16942,7 @@
       <c r="G510" t="s">
         <v>8</v>
       </c>
-      <c r="H510" s="1">
+      <c r="H510">
         <v>29669</v>
       </c>
       <c r="I510" s="1" t="s">
@@ -16965,6 +16965,9 @@
         <v>8</v>
       </c>
       <c r="G511" t="s">
+        <v>8</v>
+      </c>
+      <c r="H511" t="s">
         <v>8</v>
       </c>
     </row>
